--- a/textos-sitio-wow.xlsx
+++ b/textos-sitio-wow.xlsx
@@ -28,7 +28,29 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pronto" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Error 404" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Home alternativa" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Casos de estudio (popup)" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Lámparas Milán" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Orbit" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Ajá Waffles" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Arlo" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Tin-T!" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Moosy" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Indeleble" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Pretty Pets" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Prepapp" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Seed Capital" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - AM Studios" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Tata's Photos" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Geco." sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Epika Store" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Centro del Sueño y R" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Clínica del Cerebro" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Carlos Ravelo" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Caminos de la Vida" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - La Marquessa" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Ser Niños" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Acústica EAFIT" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Christmas House" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Walkmate" sheetId="44" state="visible" r:id="rId44"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28444,7 +28466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B176"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -28466,7 +28488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>H1 (proyecto)</t>
+          <t>H1 (nombre del proyecto)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -28478,2088 +28500,1470 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>H2 (título del caso)</t>
+          <t>Categoría</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Le cambiamos la luz, no la esencia.</t>
+          <t>Iluminación · Hogar y decoración</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Reto</t>
+          <t>Tagline</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Lámparas Milán ya tenía clientes y una marca reconocida, pero su imagen necesitaba ponerse al día y su presencia digital tenía que empezar a trabajar para vender. El reto: modernizarla sin perder lo que la hacía reconocible.</t>
+          <t>Fabrica *bellezas*</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Descripción</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Sus clientes no compran solo una lámpara: compran cómo se va a ver su casa. La marca tenía que mostrar espacios, no solo productos.</t>
+          <t>Empresa de iluminación y decoración para el hogar.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Qué construimos</t>
+          <t>Trabajo realizado</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Un refresh de marca que conserva su esencia con una imagen más actual; un sitio web donde los productos se ven en ambientes reales; y una estrategia de SEO y pauta digital para llegar a quienes están decorando o remodelando su hogar.</t>
+          <t>Refresh y rebranding de una marca existente, manteniendo sus valores y esencia. Diseño y desarrollo del sitio web, estrategia de marketing digital, pauta digital y SEO.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Aprendizaje</t>
+          <t>Capacidades (card)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Renovar no es empezar de cero: lo que la gente ya reconoce de una marca es un activo que hay que cuidar.</t>
+          <t>Identidad y diseño de marca · Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Herramientas</t>
+          <t>H2 (título del caso)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Wix, Adobe Illustrator, Semrush, Search Console, Google Analytics 4, Google My Business, Google Ads, Meta Ads</t>
+          <t>Le cambiamos la luz, no la esencia.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
+          <t>Reto</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Rebranding, Diseño web, Desarrollo web</t>
+          <t>Lámparas Milán ya tenía clientes y una marca reconocida, pero su imagen necesitaba ponerse al día y su presencia digital tenía que empezar a trabajar para vender. El reto: modernizarla sin perder lo que la hacía reconocible.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Capacidades — Insight Lab</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de marketing digital, Pauta digital, SEO</t>
+          <t>Sus clientes no compran solo una lámpara: compran cómo se va a ver su casa. La marca tenía que mostrar espacios, no solo productos.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>H1 (proyecto)</t>
+          <t>Qué construimos</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Ajá Waffles</t>
+          <t>Un refresh de marca que conserva su esencia con una imagen más actual; un sitio web donde los productos se ven en ambientes reales; y una estrategia de SEO y pauta digital para llegar a quienes están decorando o remodelando su hogar.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>H2 (título del caso)</t>
+          <t>Aprendizaje</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>¿Waffles de yuca? ¡Ajá, eso!</t>
+          <t>Renovar no es empezar de cero: lo que la gente ya reconoce de una marca es un activo que hay que cuidar.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Reto</t>
+          <t>Botón "Ver sitio" (enlace)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Ajá Waffles es un emprendimiento gastronómico nuevo con un diferencial claro: waffles a base de yuca. Sin marca ni presencia digital todavía, competía por atención frente a cafeterías ya conocidas.</t>
+          <t>https://www.cristaleriamilan.com/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Herramientas</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Su público no buscaba una cafetería más: buscaba algo distinto a las cafeterías tradicionales.</t>
+          <t>Wix, Adobe Illustrator, Semrush, Search Console, Google Analytics 4, Google My Business, Google Ads, Meta Ads</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Qué construimos</t>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Una estrategia de lanzamiento centrada en su diferencial (waffles de yuca con el sabor de la costa): un mensaje que lo pone en primer plano desde el primer contacto y contenidos pensados para despertar curiosidad en quienes buscan algo distinto a la cafetería de siempre.</t>
+          <t>Rebranding, Diseño web, Desarrollo web</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>Capacidades — Insight Lab</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marketing digital, Pauta digital, SEO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Orbit</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Moda · Ropa deportiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>*Orbita* tu pasión</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Marca de ropa deportiva de Centroamérica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Naming, logo y sistema de color construidos desde cero para posicionar a Orbit como marca de ropa deportiva en Centroamérica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>De cero a órbita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Orbit quería entrar al mercado de ropa deportiva en Centroamérica sin nada construido (ni nombre, ni logo, ni colores) y competir con marcas ya conocidas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>En ropa deportiva la gente compra identidad: quiere sentirse parte de algo cuando entrena.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Un nombre que habla de movimiento y constancia, un logo pensado para vivir en las prendas y un sistema de color con energía deportiva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>Aprendizaje</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Cuando se parte de cero, el nombre y el color son la primera promesa de la marca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Naming, Logo, Sistema de color</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Ajá Waffles</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Gastronomía</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>El sabor de la costa *en cada bocado*</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Emprendimiento de waffles a base de yuca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Ajá Waffles es un emprendimiento gastronómico nuevo con un diferencial claro: waffles a base de yuca. Necesitaban una marca desde cero que reflejara ese sabor costeño y se destacara frente a las cafeterías tradicionales. Construimos el naming, la propuesta de valor, el logo, los colores y la identidad visual, y diseñamos la estrategia de marketing digital para su lanzamiento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marca · Identidad y diseño de marca · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>¿Waffles de yuca? ¡Ajá, eso!</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Ajá Waffles es un emprendimiento gastronómico nuevo con un diferencial claro: waffles a base de yuca. Sin marca ni presencia digital todavía, competía por atención frente a cafeterías ya conocidas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Su público no buscaba una cafetería más: buscaba algo distinto a las cafeterías tradicionales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Una estrategia de lanzamiento centrada en su diferencial (waffles de yuca con el sabor de la costa): un mensaje que lo pone en primer plano desde el primer contacto y contenidos pensados para despertar curiosidad en quienes buscan algo distinto a la cafetería de siempre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Un producto diferente necesita un mensaje igual de distinto para encontrar a quien lo estaba buscando.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Herramientas</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Canva, Adobe Illustrator</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Capacidades — Insight Lab</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Estrategia de marketing digital, Estrategia de lanzamiento</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Arlo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Legal · Industrias creativas</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Para lo legal, un poco de *creatividad*</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Firma de abogados especializada en servicios legales para creativos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Definición de propuesta de valor y desarrollo de identidad visual. Organización del sistema de marca, selección de colores y construcción de Brand Book. El proyecto no incluyó el diseño del logo ni de la mascota Arlo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Abogados que hablan creativo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Arlo es una firma de abogados para creativos. Ya tenía logo y mascota, pero le faltaba una propuesta de valor clara y un sistema de marca que la hiciera coherente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Los creativos suelen ver lo legal como algo frío y lejano; la marca tenía que sentirse cercana a su mundo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Definimos su propuesta de valor, organizamos su sistema de marca, seleccionamos la paleta de color y construimos un Brand Book para que la marca se use igual en todas partes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Ordenar un sistema de marca también es diseño: a veces el trabajo es darle estructura a lo que ya existe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Propuesta de valor, Identidad visual, Sistema de marca, Brand Book</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Tin-T!</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Merchandising · Diseño colombiano</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Recuerdos que *cuentan historias*</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Emprendimiento colombiano de merchandising.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Desarrollo de la marca, incluyendo propuesta de valor e identidad visual. Creación de los personajes Cafecito y Aguacatico, concebidos como parte del universo de la marca y desarrollados para merchandising y diferentes aplicaciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Cafecito, Aguacatico y una marca con personalidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Tin-T! es un emprendimiento colombiano de merchandising. En un mercado lleno de recuerdos parecidos, necesitaba una marca que se quedara en la memoria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Un recuerdo se compra por la historia que cuenta, no por el objeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Propuesta de valor, identidad visual y dos personajes, Cafecito y Aguacatico, inspirados en íconos colombianos, diseñados para vivir en productos y aplicaciones de la marca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Los personajes convierten un producto en un recuerdo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Propuesta de valor, Identidad visual, Personajes, Merchandising</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Moosy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Moda · Comercio</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Moda con *carácter propio*.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Tienda de moda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Desarrollo de identidad visual para una tienda de moda con personalidad propia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Moda que no se viste igual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Moosy es una tienda de moda con personalidad propia, pero su imagen no lo estaba reflejando.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>En moda, la identidad visual es lo primero que el cliente "se prueba".</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Una identidad visual con carácter, pensada para destacar en redes y en la tienda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Una tienda con personalidad propia necesita una identidad que no se parezca a las demás.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Identidad visual</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Indeleble</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Servicios profesionales · Contabilidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>La huella *indeleble* de tus finanzas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Firma contable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>El punto de partida fue el nombre: le dimos identidad a esta firma contable con un sistema visual construido a partir de su naming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Un nombre que deja huella, una marca que no se borra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Indeleble, una firma contable, ya tenía un nombre con fuerza, pero no una identidad visual que lo respaldara en un sector que suele verse igual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>El nombre ya contaba una historia: una huella que no se borra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Un sistema visual construido a partir del nombre: la idea de una huella que no se borra, traducida en logo, colores y aplicaciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Cuando el nombre es fuerte, la identidad tiene que amplificarlo, no competir con él.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Identidad visual, Sistema visual</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Pretty Pets</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Mascotas · Comercio</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>*Pretty,* así como tu mascota</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Tienda de artículos para mascotas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Identidad de marca para una tienda de mascotas, acompañada de estrategia y pauta digital para llevar esa identidad a sus canales de venta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Identidad y diseño de marca · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>H2 (título del caso)</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Visitas que mueven la cola.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Reto</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Pretty Pets tenía productos y canales de venta, pero necesitaba que llegaran a ellos personas realmente interesadas en comprar para sus mascotas.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Insight</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Quien compra para su mascota compra con el corazón, y lo hace en los canales donde ya confía.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Qué construimos</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Una estrategia digital que parte de las mascotas y sus dueños, no del catálogo, y campañas de pauta segmentadas por intereses que llevan directo a sus canales de venta.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Aprendizaje</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>La pauta rinde más cuando lleva a la gente a donde ya compra, no a un canal nuevo.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Herramientas</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Meta Ads</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Capacidades — Insight Lab</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Estrategia digital, Pauta digital</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Geco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Verde de verdad, no de discurso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>Geco. vende productos ecológicos en un mercado donde muchas marcas dicen ser "verdes". Necesitaba atraer a un público consciente y lograr que ese interés terminara en una compra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>El público consciente desconfía de lo que es "verde" solo de palabra: necesita razones claras para elegir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Una estrategia digital que explica con claridad por qué cada producto es una mejor elección, con un tono cercano y sin sermones, y un recorrido pensado para pasar del interés a la compra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>En lo sostenible, la coherencia vende más que el discurso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>Shopify, Meta Ads, Google Ads</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Insight Lab</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Estrategia de marketing digital</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Epika Store</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Orlando, a un clic de distancia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Epika Store trae productos de Disney Parks y Universal Studios desde Orlando. Tenía un producto que enamora, pero necesitaba llegar a los fans y convertir ese entusiasmo en ventas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Sus clientes no buscan un producto: buscan un pedacito de la experiencia de los parques sin viajar a Orlando.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Todo el recorrido, desde el desarrollo de marca y el logo hasta el sitio, los posts para redes y la pauta digital: una estrategia que vende la experiencia antes que el objeto, con contenidos que evocan los parques y campañas dirigidas a fans de Disney y Universal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Cuando el producto es emoción, la comunicación tiene que vender la experiencia, no el objeto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Lynka, Meta Ads</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Desarrollo de marca, Logo, Sitio web</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Insight Lab</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Estrategia de marketing digital, Contenido para redes, Pauta digital</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Centro del Sueño y Ronquido</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Despiertos cuando alguien busca por qué ronca.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>El Centro del Sueño y Ronquido es un centro especializado en Medellín. Necesitaba que las personas con problemas de sueño lo encontraran justo cuando empiezan a buscar respuestas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>Quien ronca o duerme mal suele buscar respuestas en internet antes de pedir una cita.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Un sitio web claro, pensado para resolver dudas y agendar; un blog con artículos sobre ronquido, apnea y trastornos del sueño optimizados para SEO; y pauta digital para llegar a pacientes en Medellín.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>Resultado</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Subimos 58 puestos en el ranking de Google en menos de 3 semanas, con SEO, GEO, AEO y optimización de Google My Business.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>En salud, un sitio claro y confiable es el primer paso de la consulta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Wix, Semrush, Search Console, Google Analytics 4, Google My Business, Google Ads, Meta Ads</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Sitio web</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Insight Lab</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Estrategia de marketing digital, Pauta digital, SEO, Blog y contenidos</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Clínica del Cerebro</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>Claridad para decisiones que pesan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>La Clínica del Cerebro atiende pacientes neurológicos en Medellín. Sus pacientes y sus familias llegan con dudas y preocupación, y la clínica necesitaba un canal digital que les diera confianza antes de la primera cita.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>Los pacientes y sus familias llegan con dudas y preocupación: necesitan información clara antes de agendar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>Un sitio web que explica sus servicios en lenguaje sencillo, contenido educativo para redes sociales sobre temas neurológicos y pauta digital para llegar a pacientes en Medellín.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>En salud, la confianza se construye con información útil, no con promesas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>Wix, Meta Ads</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>Diseño web</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Insight Lab</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>Estrategia de marketing digital, Pauta digital, Contenido para redes</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>Caminos de la Vida</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Tranquilidad para quien decide por amor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>Caminos de la Vida es un hogar geriátrico. Elegir un hogar para un padre o una madre es una decisión difícil, y necesitaba que las familias lo encontraran y confiaran en él.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Quien decide casi nunca es el adulto mayor, sino su familia, y lo que busca es tranquilidad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>Un sitio web que muestra el día a día del hogar y responde las preguntas de las familias, y una estrategia de marketing y pauta digital dirigida a hijos y familiares que están buscando opciones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Cuando la decisión es emocional, la comunicación tiene que hablarle a quien decide.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>Google Ads, Meta Ads</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Desarrollo web</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Insight Lab</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>Estrategia de marketing digital, Pauta digital</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>La Marquessa</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>Primero la vitrina, después la fila.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>La Marquessa ya vendía accesorios en su tienda en línea y quería vender más. Invertir en pauta sin revisar el sitio era arriesgarse a pagar por visitas que no compran.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>Llevar más visitas a un sitio que no está listo para vender es pagar dos veces: primero había que ajustar el sitio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>Optimizamos el sitio para que comprar fuera más fácil (navegación, fichas de producto y proceso de compra) y después diseñamos una estrategia de pauta digital para llevar tráfico a una tienda lista para vender.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>Primero se optimiza la tienda, después se invierte en pauta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>Vercel, GitHub, Google My Business, Meta Ads</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Optimización del sitio web</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Insight Lab</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>Pauta digital</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>Ser Niños</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Un solo juego: vender más.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>Ser Niños es una tienda de juguetes y educación consciente con sitio propio. Su objetivo era claro: vender más en línea.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Las familias que buscan juguetes conscientes investigan antes de comprar: el sitio tenía que resolver sus dudas rápido.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>Ajustes puntuales al sitio para que las familias encuentren rápido lo que buscan y entiendan el valor de cada juguete, y una estrategia de pauta digital medida contra un solo objetivo: las ventas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Un solo objetivo hace que cada ajuste y cada peso de pauta se midan contra lo mismo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>Vercel, GitHub, Google My Business, Meta Ads</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Ajustes al sitio web</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Insight Lab</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>Pauta digital</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Orbit</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>De cero a órbita.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Orbit quería entrar al mercado de ropa deportiva en Centroamérica sin nada construido (ni nombre, ni logo, ni colores) y competir con marcas ya conocidas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>En ropa deportiva la gente compra identidad: quiere sentirse parte de algo cuando entrena.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Un nombre que habla de movimiento y constancia, un logo pensado para vivir en las prendas y un sistema de color con energía deportiva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>Cuando se parte de cero, el nombre y el color son la primera promesa de la marca.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Adobe Illustrator</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>Naming, Logo, Sistema de color</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Arlo</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>Abogados que hablan creativo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Arlo es una firma de abogados para creativos. Ya tenía logo y mascota, pero le faltaba una propuesta de valor clara y un sistema de marca que la hiciera coherente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>Los creativos suelen ver lo legal como algo frío y lejano; la marca tenía que sentirse cercana a su mundo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>Definimos su propuesta de valor, organizamos su sistema de marca, seleccionamos la paleta de color y construimos un Brand Book para que la marca se use igual en todas partes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>Ordenar un sistema de marca también es diseño: a veces el trabajo es darle estructura a lo que ya existe.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>Adobe Illustrator</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Propuesta de valor, Identidad visual, Sistema de marca, Brand Book</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>Tin-T!</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>Cafecito, Aguacatico y una marca con personalidad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>Tin-T! es un emprendimiento colombiano de merchandising. En un mercado lleno de recuerdos parecidos, necesitaba una marca que se quedara en la memoria.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>Un recuerdo se compra por la historia que cuenta, no por el objeto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Propuesta de valor, identidad visual y dos personajes, Cafecito y Aguacatico, inspirados en íconos colombianos, diseñados para vivir en productos y aplicaciones de la marca.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>Los personajes convierten un producto en un recuerdo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Adobe Illustrator</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>Propuesta de valor, Identidad visual, Personajes, Merchandising</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>Moosy</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>Moda que no se viste igual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>Moosy es una tienda de moda con personalidad propia, pero su imagen no lo estaba reflejando.</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>En moda, la identidad visual es lo primero que el cliente "se prueba".</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Una identidad visual con carácter, pensada para destacar en redes y en la tienda.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>Una tienda con personalidad propia necesita una identidad que no se parezca a las demás.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Adobe Illustrator</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>Identidad visual</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Indeleble</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>Un nombre que deja huella, una marca que no se borra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>Indeleble, una firma contable, ya tenía un nombre con fuerza, pero no una identidad visual que lo respaldara en un sector que suele verse igual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>El nombre ya contaba una historia: una huella que no se borra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>Un sistema visual construido a partir del nombre: la idea de una huella que no se borra, traducida en logo, colores y aplicaciones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>Cuando el nombre es fuerte, la identidad tiene que amplificarlo, no competir con él.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>Adobe Illustrator</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>Identidad visual, Sistema visual</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>Prepapp</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>Estudiar para el examen, pero con amigos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>Prepapp es una app enfocada en preparar estudiantes para exámenes de Estado. El reto no era solo la marca, sino construir un universo propio que la hiciera cercana a su público joven.</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>Para un estudiante, prepararse para un examen es una obligación; la marca tenía que hacerlo sentir más cercano y menos pesado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Naming, propuesta de valor, identidad visual, logo y colores, y un sistema de personajes que acompaña al estudiante y le da a la app personalidad más allá de la funcionalidad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>Los personajes le dan a una app algo que la funcionalidad sola no da: cercanía.</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>Adobe Illustrator</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>Naming, Propuesta de valor, Identidad visual, Logo, Personajes</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>Seed Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>Una semilla que se escucha.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>Seed Capital es un podcast de emprendimiento que necesitaba una marca con presencia propia frente a otros medios del sector.</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>Entre muchos podcasts de emprendimiento, lo que el público recuerda es la marca, no solo el tema.</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>Naming, propuesta de valor y sistema de identidad visual (logo, colores y aplicaciones) pensados para funcionar tanto en el podcast como en sus redes y piezas de difusión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>Una identidad pensada desde el inicio para redes y piezas de difusión trabaja en todos los canales.</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>Adobe Illustrator</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>Naming, Propuesta de valor, Identidad visual, Piezas para redes</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>AM Studios</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>Diseñar con datos, y que se note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>AM Studios es una agencia de marketing digital con buenos resultados, pero su marca no lo transmitía: necesitaba verse tan sólida como su trabajo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>Una agencia que vende resultados no puede tener una marca improvisada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>Desde el naming, construimos el logo, la paleta de color y una identidad visual con un lenguaje que une diseño y datos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>La marca de una agencia es su primera muestra de trabajo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>Adobe Illustrator</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>Logo, Paleta de color, Identidad visual</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>Tata's Photos</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>Una marca tan detallista como su lente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>Una fotógrafa que quería dejar de ser "una fotógrafa más" y tener una marca personal que la representara.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>En fotografía, la gente contrata a la persona, no solo el servicio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>Definimos su propuesta de valor y construimos el naming, los colores y una identidad inspirada en su forma de mirar: encontrar la belleza en las cosas pequeñas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>Una marca personal funciona cuando se parece a quien la lleva.</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>Marca personal, Propuesta de valor, Naming, Identidad visual</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>Carlos Ravelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>Solidez que se ve antes de la primera reunión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>Carlos Ravelo es consultor de estrategia de negocios. En consultoría la primera impresión pesa: su marca tenía que transmitir la misma solidez que su asesoría.</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>Un consultor vende confianza antes de vender su asesoría.</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>Una identidad visual sobria y profesional, pensada para sus presentaciones, propuestas y redes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>La marca personal tiene que transmitir lo mismo que la persona en una reunión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>Adobe Illustrator</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>Marca personal, Identidad visual</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>H1 (proyecto)</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>Walkmate</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>Amor a primer paseo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>Walkmate es una empresa de paseo de perros en Australia. Quien la contrata le confía a su perro: la marca tenía que transmitir cariño y confianza desde el primer vistazo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>Quien contrata un paseador deja a su perro en manos de otro: la marca tenía que transmitir confianza y cariño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>Una identidad de marca cercana y amigable, pensada para funcionar en todos sus puntos de contacto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>En servicios de cuidado, la identidad tiene que inspirar confianza desde el primer vistazo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>Adobe Illustrator</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>Identidad de marca</t>
         </is>
       </c>
     </row>
@@ -33742,6 +33146,1926 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Prepapp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Educación · Tecnología</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Prepárate para la *siguiente etapa*</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Aplicación enfocada en la preparación para exámenes de Estado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Prepapp es una app enfocada en preparar estudiantes para exámenes de Estado. El reto no era solo la marca, sino construir un universo propio que la hiciera cercana a su público joven: naming, propuesta de valor, identidad visual, logo, colores y un sistema de personajes que le dieran personalidad a la app más allá de la funcionalidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Estudiar para el examen, pero con amigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Prepapp es una app enfocada en preparar estudiantes para exámenes de Estado. El reto no era solo la marca, sino construir un universo propio que la hiciera cercana a su público joven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Para un estudiante, prepararse para un examen es una obligación; la marca tenía que hacerlo sentir más cercano y menos pesado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Naming, propuesta de valor, identidad visual, logo y colores, y un sistema de personajes que acompaña al estudiante y le da a la app personalidad más allá de la funcionalidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Los personajes le dan a una app algo que la funcionalidad sola no da: cercanía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Naming, Propuesta de valor, Identidad visual, Logo, Personajes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Seed Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Medios · Emprendimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>*Descubre* la semilla del éxito</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Podcast enfocado en emprendimiento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Seed Capital es un podcast de emprendimiento que necesitaba una marca con presencia propia frente a otros medios del sector. Trabajamos el naming, la propuesta de valor y el sistema de identidad visual (logo, colores y aplicaciones) pensados para funcionar tanto en el podcast como en sus redes y piezas de difusión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Una semilla que se escucha.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Seed Capital es un podcast de emprendimiento que necesitaba una marca con presencia propia frente a otros medios del sector.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Entre muchos podcasts de emprendimiento, lo que el público recuerda es la marca, no solo el tema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Naming, propuesta de valor y sistema de identidad visual (logo, colores y aplicaciones) pensados para funcionar tanto en el podcast como en sus redes y piezas de difusión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Una identidad pensada desde el inicio para redes y piezas de difusión trabaja en todos los canales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Naming, Propuesta de valor, Identidad visual, Piezas para redes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>AM Studios</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Marketing digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Diseña *con datos*</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Agencia de marketing digital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Una agencia de marketing digital necesitaba verse tan sólida como sus resultados: logo, paleta de color e identidad visual construidos desde el naming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Diseñar con datos, y que se note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>AM Studios es una agencia de marketing digital con buenos resultados, pero su marca no lo transmitía: necesitaba verse tan sólida como su trabajo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Una agencia que vende resultados no puede tener una marca improvisada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Desde el naming, construimos el logo, la paleta de color y una identidad visual con un lenguaje que une diseño y datos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>La marca de una agencia es su primera muestra de trabajo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Logo, Paleta de color, Identidad visual</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Tata's Photos</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Fotografía</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Find the beauty *in the small things*</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Marca personal de fotografía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Marca personal para una fotógrafa: definimos su propuesta de valor y construimos el naming, los colores y la identidad que la representan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Una marca tan detallista como su lente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Una fotógrafa que quería dejar de ser "una fotógrafa más" y tener una marca personal que la representara.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>En fotografía, la gente contrata a la persona, no solo el servicio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Definimos su propuesta de valor y construimos el naming, los colores y una identidad inspirada en su forma de mirar: encontrar la belleza en las cosas pequeñas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Una marca personal funciona cuando se parece a quien la lleva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Marca personal, Propuesta de valor, Naming, Identidad visual</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Geco.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Comercio · Sostenibilidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Get eco *like a geko*</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Tienda de productos ecológicos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Identidad visual para una tienda de productos ecológicos, con una estrategia digital pensada para atraer a un público consciente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Identidad y diseño de marca · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Verde de verdad, no de discurso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Geco. vende productos ecológicos en un mercado donde muchas marcas dicen ser "verdes". Necesitaba atraer a un público consciente y lograr que ese interés terminara en una compra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>El público consciente desconfía de lo que es "verde" solo de palabra: necesita razones claras para elegir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Una estrategia digital que explica con claridad por qué cada producto es una mejor elección, con un tono cercano y sin sermones, y un recorrido pensado para pasar del interés a la compra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>En lo sostenible, la coherencia vende más que el discurso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Shopify, Meta Ads, Google Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Insight Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marketing digital</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Epika Store</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Comercio · Entretenimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Magia y estilo de *Disney* y *Universal*.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Tienda de productos traídos de Disney Parks y Universal Studios en Orlando.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Desarrollo de logo, colores, sistema de identidad, tarjetas, texturas y diferentes aplicaciones de marca. Desarrollo de estrategia de marketing digital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Identidad y diseño de marca · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Orlando, a un clic de distancia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Epika Store trae productos de Disney Parks y Universal Studios desde Orlando. Tenía un producto que enamora, pero necesitaba llegar a los fans y convertir ese entusiasmo en ventas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sus clientes no buscan un producto: buscan un pedacito de la experiencia de los parques sin viajar a Orlando.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Todo el recorrido, desde el desarrollo de marca y el logo hasta el sitio, los posts para redes y la pauta digital: una estrategia que vende la experiencia antes que el objeto, con contenidos que evocan los parques y campañas dirigidas a fans de Disney y Universal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Cuando el producto es emoción, la comunicación tiene que vender la experiencia, no el objeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Botón "Ver sitio" (enlace)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lynka.io/s/epika-store</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Lynka, Meta Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Desarrollo de marca, Logo, Sitio web</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Insight Lab</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marketing digital, Contenido para redes, Pauta digital</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Centro del Sueño y Ronquido</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Salud · Sueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Centro especializado en sueño en Medellín.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Sitio web, estrategia de marketing digital y pauta digital para un centro especializado en sueño en Medellín.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Despiertos cuando alguien busca por qué ronca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>El Centro del Sueño y Ronquido es un centro especializado en Medellín. Necesitaba que las personas con problemas de sueño lo encontraran justo cuando empiezan a buscar respuestas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Quien ronca o duerme mal suele buscar respuestas en internet antes de pedir una cita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Un sitio web claro, pensado para resolver dudas y agendar; un blog con artículos sobre ronquido, apnea y trastornos del sueño optimizados para SEO; y pauta digital para llegar a pacientes en Medellín.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Subimos 58 puestos en el ranking de Google en menos de 3 semanas, con SEO, GEO, AEO y optimización de Google My Business.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>En salud, un sitio claro y confiable es el primer paso de la consulta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Botón "Ver sitio" (enlace)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clinicadelsuenoyronquido.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Wix, Semrush, Search Console, Google Analytics 4, Google My Business, Google Ads, Meta Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Sitio web</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Insight Lab</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marketing digital, Pauta digital, SEO, Blog y contenidos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Clínica del Cerebro</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Salud · Neurología</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Una mente sana *para un futuro brillante*</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Clínica neurológica en Medellín.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Rebranding, diseño de sitio web, estrategia de marketing digital y pauta digital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marca · Identidad y diseño de marca · Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Claridad para decisiones que pesan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>La Clínica del Cerebro atiende pacientes neurológicos en Medellín. Sus pacientes y sus familias llegan con dudas y preocupación, y la clínica necesitaba un canal digital que les diera confianza antes de la primera cita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Los pacientes y sus familias llegan con dudas y preocupación: necesitan información clara antes de agendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Un sitio web que explica sus servicios en lenguaje sencillo, contenido educativo para redes sociales sobre temas neurológicos y pauta digital para llegar a pacientes en Medellín.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>En salud, la confianza se construye con información útil, no con promesas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Wix, Meta Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Diseño web</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Insight Lab</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marketing digital, Pauta digital, Contenido para redes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Ravelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Consultoría de negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Consultor de *estrategia de negocios*.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Consultor de estrategia de negocios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Marca personal para un consultor de estrategia de negocios: definimos su identidad visual para transmitir la misma solidez que su asesoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Solidez que se ve antes de la primera reunión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Ravelo es consultor de estrategia de negocios. En consultoría la primera impresión pesa: su marca tenía que transmitir la misma solidez que su asesoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Un consultor vende confianza antes de vender su asesoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Una identidad visual sobria y profesional, pensada para sus presentaciones, propuestas y redes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>La marca personal tiene que transmitir lo mismo que la persona en una reunión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Marca personal, Identidad visual</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Caminos de la Vida</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Salud · Cuidado del adulto mayor</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Hogar geriátrico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marketing digital, pauta digital y desarrollo de sitio web para un hogar geriátrico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Tranquilidad para quien decide por amor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Caminos de la Vida es un hogar geriátrico. Elegir un hogar para un padre o una madre es una decisión difícil, y necesitaba que las familias lo encontraran y confiaran en él.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Quien decide casi nunca es el adulto mayor, sino su familia, y lo que busca es tranquilidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Un sitio web que muestra el día a día del hogar y responde las preguntas de las familias, y una estrategia de marketing y pauta digital dirigida a hijos y familiares que están buscando opciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Cuando la decisión es emocional, la comunicación tiene que hablarle a quien decide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Botón "Ver sitio" (enlace)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.hogarcaminosdelavida.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Google Ads, Meta Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Desarrollo web</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Insight Lab</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marketing digital, Pauta digital</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -35828,6 +37152,720 @@
       <c r="B173" s="2" t="inlineStr">
         <is>
           <t>Hecho con asombro ✦</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>La Marquessa</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Moda · Accesorios</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tienda de accesorios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Optimizamos el sitio web de esta tienda de accesorios y diseñamos la estrategia de pauta digital para impulsar sus ventas online.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Primero la vitrina, después la fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>La Marquessa ya vendía accesorios en su tienda en línea y quería vender más. Invertir en pauta sin revisar el sitio era arriesgarse a pagar por visitas que no compran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Llevar más visitas a un sitio que no está listo para vender es pagar dos veces: primero había que ajustar el sitio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Optimizamos el sitio para que comprar fuera más fácil (navegación, fichas de producto y proceso de compra) y después diseñamos una estrategia de pauta digital para llevar tráfico a una tienda lista para vender.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Primero se optimiza la tienda, después se invierte en pauta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Vercel, GitHub, Google My Business, Meta Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Optimización del sitio web</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Insight Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Pauta digital</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Ser Niños</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Comercio · Educación</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tienda de juguetes y educación consciente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Ajustes al sitio web y una estrategia de pauta digital enfocada en un solo objetivo: que esta tienda de juguetes venda más.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Un solo juego: vender más.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Ser Niños es una tienda de juguetes y educación consciente con sitio propio. Su objetivo era claro: vender más en línea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Las familias que buscan juguetes conscientes investigan antes de comprar: el sitio tenía que resolver sus dudas rápido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Ajustes puntuales al sitio para que las familias encuentren rápido lo que buscan y entiendan el valor de cada juguete, y una estrategia de pauta digital medida contra un solo objetivo: las ventas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Un solo objetivo hace que cada ajuste y cada peso de pauta se midan contra lo mismo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Vercel, GitHub, Google My Business, Meta Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Ajustes al sitio web</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Insight Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Pauta digital</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Acústica EAFIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Sitio web</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sitio web desarrollado en WordPress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Christmas House</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Comercio</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tienda en línea con pauta digital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Walkmate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Cuidado de mascotas · Australia</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>*Empresa de paseo* de perros en Australia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Empresa de paseo de perros en Australia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Identidad de marca diseñada para una empresa de paseo de perros en Australia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Amor a primer paseo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Walkmate es una empresa de paseo de perros en Australia. Quien la contrata le confía a su perro: la marca tenía que transmitir cariño y confianza desde el primer vistazo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Quien contrata un paseador deja a su perro en manos de otro: la marca tenía que transmitir confianza y cariño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Una identidad de marca cercana y amigable, pensada para funcionar en todos sus puntos de contacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>En servicios de cuidado, la identidad tiene que inspirar confianza desde el primer vistazo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Identidad de marca</t>
         </is>
       </c>
     </row>

--- a/textos-sitio-wow.xlsx
+++ b/textos-sitio-wow.xlsx
@@ -34,29 +34,30 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Textos de JavaScript" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Admin (panel interno)" sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="llms.txt" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Lámparas Milán" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Orbit" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Ajá Waffles" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Arlo" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Tin-T!" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Moosy" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Indeleble" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Pretty Pets" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Prepapp" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Seed Capital" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - AM Studios" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Tata's Photos" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Geco." sheetId="40" state="visible" r:id="rId40"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Epika Store" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Centro del Sueño y R" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Clínica del Cerebro" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Carlos Ravelo" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Caminos de la Vida" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - La Marquessa" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Ser Niños" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Acústica EAFIT" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Christmas House" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Walkmate" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ocultos, tooltips y SEO" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Lámparas Milán" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Orbit" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Ajá Waffles" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Arlo" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Tin-T!" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Moosy" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Indeleble" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Pretty Pets" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Prepapp" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Seed Capital" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - AM Studios" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Tata's Photos" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Geco." sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Epika Store" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Centro del Sueño y R" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Clínica del Cerebro" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Carlos Ravelo" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Caminos de la Vida" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - La Marquessa" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Ser Niños" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Acústica EAFIT" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Christmas House" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyecto - Walkmate" sheetId="51" state="visible" r:id="rId51"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22964,7 +22965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -22986,180 +22987,4620 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>H1 (nombre del proyecto)</t>
+          <t>Menú / footer / popups (todas las páginas) — Tooltip (title al pasar el mouse)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Lámparas Milán</t>
+          <t>Sitios web, landing pages y tiendas en línea con una estética que representa tu marca.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Categoría</t>
+          <t>Menú / footer / popups (todas las páginas) — Tooltip (title al pasar el mouse)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Iluminación · Hogar y decoración</t>
+          <t>Interfaces claras y experiencias de usuario pensadas de principio a fin.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Tagline</t>
+          <t>Menú / footer / popups (todas las páginas) — Tooltip (title al pasar el mouse)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Fabrica *bellezas*</t>
+          <t>Tiendas en línea listas para vender, del catálogo al checkout.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Descripción</t>
+          <t>Menú / footer / popups (todas las páginas) — Tooltip (title al pasar el mouse)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Empresa de iluminación y decoración para el hogar.</t>
+          <t>Piezas gráficas para redes, presentaciones y material digital, con la misma estética de tu sitio.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Trabajo realizado</t>
+          <t>Menú / footer / popups (todas las páginas) — Tooltip (title al pasar el mouse)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Refresh y rebranding de una marca existente, manteniendo sus valores y esencia. Diseño y desarrollo del sitio web, estrategia de marketing digital, pauta digital y SEO.</t>
+          <t>Investigamos las palabras clave correctas y posicionamos tu sitio para que te encuentren cuando te buscan.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Capacidades (card)</t>
+          <t>Menú / footer / popups (todas las páginas) — Tooltip (title al pasar el mouse)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Identidad y diseño de marca · Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+          <t>Optimizamos tu perfil de Google Business y tu presencia local para que te encuentren cerca.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>H2 (título del caso)</t>
+          <t>Menú / footer / popups (todas las páginas) — Tooltip (title al pasar el mouse)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Le cambiamos la luz, no la esencia.</t>
+          <t>Optimizamos tu marca para aparecer en las respuestas de ChatGPT, Google AI y otros buscadores con IA.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Reto</t>
+          <t>Menú / footer / popups (todas las páginas) — Tooltip (title al pasar el mouse)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Lámparas Milán ya tenía clientes y una marca reconocida, pero su imagen necesitaba ponerse al día y su presencia digital tenía que empezar a trabajar para vender. El reto: modernizarla sin perder lo que la hacía reconocible.</t>
+          <t>Maximizamos las conversiones de tu sitio con pruebas y optimización continua.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Menú / footer / popups (todas las páginas) — Tooltip (title al pasar el mouse)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sus clientes no compran solo una lámpara: compran cómo se va a ver su casa. La marca tenía que mostrar espacios, no solo productos.</t>
+          <t>Pauta y campañas en Meta, Google y TikTok, con una estrategia detrás: la segmentación de audiencia correcta y mensajes coordinados para lanzar con fuerza.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Qué construimos</t>
+          <t>Menú / footer / popups (todas las páginas) — Tooltip (title al pasar el mouse)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Un refresh de marca que conserva su esencia con una imagen más actual; un sitio web donde los productos se ven en ambientes reales; y una estrategia de SEO y pauta digital para llegar a quienes están decorando o remodelando su hogar.</t>
+          <t>Convertimos el tráfico de tu sitio en decisiones: qué está funcionando, qué no, y qué cambiar primero.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Aprendizaje</t>
+          <t>Menú / footer / popups (todas las páginas) — Tooltip (title al pasar el mouse)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Renovar no es empezar de cero: lo que la gente ya reconoce de una marca es un activo que hay que cuidar.</t>
+          <t>Dashboards claros que traducen tus datos en decisiones, sin depender de hojas de cálculo.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Botón "Ver sitio" (enlace)</t>
+          <t>Menú / footer / popups (todas las páginas) — Tooltip (title al pasar el mouse)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://www.cristaleriamilan.com/</t>
+          <t>Configuramos GA4, Tag Manager y eventos de conversión: la base técnica sin la que no hay datos que analizar.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Herramientas</t>
+          <t>Menú / footer / popups (todas las páginas) — Tooltip (title al pasar el mouse)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Wix, Adobe Illustrator, Semrush, Search Console, Google Analytics 4, Google My Business, Google Ads, Meta Ads</t>
+          <t>Te ayudamos a decidir qué medir y por qué, no solo a entregarte un dashboard.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
+          <t>Menú / footer / popups (todas las páginas) — Texto de accesibilidad (aria-label)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Rebranding, Diseño web, Desarrollo web</t>
+          <t>Abrir menú</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Capacidades — Insight Lab</t>
+          <t>Menú / footer / popups (todas las páginas) — Texto de accesibilidad (aria-label)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de marketing digital, Pauta digital, SEO</t>
+          <t>Cerrar menú</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Menú / footer / popups (todas las páginas) — Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Cerrar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Menú / footer / popups (todas las páginas) — Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Anterior</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Menú / footer / popups (todas las páginas) — Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Siguiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Menú / footer / popups (todas las páginas) — Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders: inicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Menú / footer / popups (todas las páginas) — Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Menú / footer / popups (todas las páginas) — Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Menú / footer / popups (todas las páginas) — Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Menú / footer / popups (todas las páginas) — Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Explora</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Ver más</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Ver logo completo de Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Mapa del mundo con los lugares donde hemos trabajado</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Agencia de Marketing Digital y Diseño Web | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Agencia de marketing digital especializada en diseño web, desarrollo de sitios y e-commerce, SEO, SEM, pauta digital y analítica de datos. Un solo equipo, de principio a fin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Agencia de Marketing Digital y Diseño Web | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Agencia de marketing digital especializada en diseño web, desarrollo de sitios y e-commerce, SEO, SEM, pauta digital y analítica de datos. Un solo equipo, de principio a fin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Datos Google (ProfessionalService): name</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Datos Google (ProfessionalService): description</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Agencia de marketing digital especializada en diseño web, desarrollo de sitios y e-commerce, SEO, SEM, pauta digital y analítica de datos. Un solo equipo, de principio a fin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué servicios ofrece Workshop of Wonders?</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Diseño y desarrollo web (sitios, UX/UI, e-commerce y diseño gráfico), crecimiento con datos (SEO, pauta digital, CRO y analítica). Puedes contratar un servicio puntual o el proyecto completo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuánto tiempo toma un proyecto?</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Un sitio web institucional suele tomar entre 3 y 6 semanas; un e-commerce, entre 6 y 10. Los proyectos de SEO y pauta digital se acuerdan por fases para que veas avances desde las primeras semanas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>¿Trabajan con marcas de cualquier país?</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>[Home] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Sí. Trabajamos 100% remoto con clientes en Colombia, Latinoamérica y otros países. Todo el proceso se coordina por videollamada y herramientas colaborativas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Categorías de servicios</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: Diseño web</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: UX/UI Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: E-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: Diseño gráfico</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: SEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: SEO local &amp; Google Business Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: GEO (posicionamiento en IA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: CRO (Optimización de la Tasa de Conversión)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: Pauta digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: Análisis de métricas de sitios web</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: Reportería y dashboards</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: Configuración de analítica y tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: Consultoría de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: Cursos digitales</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Servicios de Diseño Web, SEO y Marketing Digital | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Diseño web, desarrollo de sitios y e-commerce, SEO, SEM, pauta digital, diseño gráfico, analítica de datos y cursos digitales: todo en una misma agencia de marketing digital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Servicios de Diseño Web, SEO y Marketing Digital | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Diseño web, desarrollo de sitios y e-commerce, SEO, SEM, pauta digital, diseño gráfico, analítica de datos y cursos digitales: todo en una misma agencia de marketing digital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Diseño web, desarrollo web, SEO y marketing digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué servicios ofrece Workshop of Wonders?</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Trabajamos en tres frentes conectados: desarrollo web (diseño, UX/UI, e-commerce y diseño gráfico), crecimiento con datos (SEO, SEM/pauta digital, CRO y analítica) y cursos digitales para que tu equipo maneje esas herramientas por su cuenta. Puedes contratar un servicio puntual o un proyecto integral de principio a fin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuánto cuesta un proyecto de diseño web o marketing digital?</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Depende del alcance: un sitio institucional no cuesta lo mismo que un e-commerce, y una campaña puntual no cuesta lo mismo que una estrategia de crecimiento integral. Cuéntanos tu proyecto y te compartimos una propuesta ajustada a tu presupuesto y objetivos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuánto tiempo toma un proyecto?</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Un sitio web suele tomar entre 3 y 6 semanas; una estrategia de SEO o pauta digital empieza a mostrar resultados medibles en 1 a 3 meses. Los proyectos integrales se acuerdan por fases para que veas avances desde las primeras semanas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>¿Trabajan con marcas de cualquier país?</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Sí. Trabajamos 100% remoto con clientes en Colombia, Latinoamérica y otros países. Todo el proceso se coordina por videollamada y herramientas colaborativas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>¿Usan inteligencia artificial en su proceso?</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Sí, la IA es una herramienta más dentro de nuestro flujo de trabajo: acelera investigación, exploración visual y producción, pero la estrategia, el criterio y la dirección creativa siguen siendo 100% humanos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>¿Puedo contratar solo un servicio, como SEO o diseño web?</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>[Servicios] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Claro. Aunque muchos clientes empiezan con un proyecto integral, también trabajamos servicios puntuales como SEO, pauta digital o el diseño de un sitio, sin necesidad de contratar todo el paquete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>[Portafolio] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>[Portafolio] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Portafolio de Marcas | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>[Portafolio] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Branding, diseño web y campañas digitales para más de 20 marcas en Colombia y Latinoamérica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>[Portafolio] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>[Portafolio] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Portafolio de Marcas | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>[Portafolio] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Branding, diseño web y campañas digitales para más de 20 marcas en Colombia y Latinoamérica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>[Portafolio] Datos Google (CollectionPage): name</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Portafolio de Marcas | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Diseño Web y Desarrollo de Sitios | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Diseño y desarrollo de sitios web conectando estrategia, UX/UI, contenido, SEO y conversión desde el principio. Un solo equipo, de principio a fin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Diseño Web y Desarrollo de Sitios | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Diseño y desarrollo de sitios web conectando estrategia, UX/UI, contenido, SEO y conversión desde el principio. Un solo equipo, de principio a fin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google (Service): name</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Diseño web y desarrollo de sitios</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Diseño web, desarrollo web y UX/UI</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google (Service): description</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Diseño y desarrollo de sitios web conectando estrategia, UX/UI, contenido, SEO y conversión desde el principio. Un solo equipo, de principio a fin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuánto cuesta un sitio web?</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Depende del alcance: no cuesta lo mismo una landing page que un sitio institucional o una tienda en línea. Cuéntanos tu proyecto y te compartimos una propuesta ajustada a tu presupuesto y objetivos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuánto tiempo toma diseñar y desarrollar un sitio web?</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Un sitio institucional suele tomar entre 3 y 6 semanas y un e-commerce entre 6 y 10; una landing page, menos. Te damos un cronograma concreto una vez definimos juntos el alcance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>¿El sitio queda optimizado para SEO desde el diseño?</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Sí. Estructuramos encabezados, metadatos, velocidad de carga y datos estructurados desde el desarrollo, para que el trabajo de SEO posterior parta de una base técnica sólida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>¿Pueden rediseñar un sitio que ya existe?</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>Sí, trabajamos tanto proyectos desde cero como rediseños de sitios existentes, migrando el contenido y cuidando el SEO ya ganado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué pasa después de lanzar una web?</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>Esta es una parte que muchas agencias dejan fuera. Nosotros creemos que el lanzamiento no debería ser el final del proyecto: es el comienzo del aprendizaje. Una página puede tener una excelente apariencia y aun así descubrir, después de algunas semanas de datos, que una determinada sección no está ayudando a convertir. Ese aprendizaje es valioso: lo utilizamos para decidir qué optimizar después.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué diferencia hay entre diseño web, UX/UI y desarrollo web?</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>Diseño web define la experiencia completa del sitio. UX/UI trabaja cómo las personas entienden, recorren e interactúan con esa experiencia. Desarrollo web convierte esa experiencia diseñada en un producto digital funcional. En WOW los tres pueden trabajar conectados para evitar que cada decisión se tome por separado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué otros servicios pueden potenciar tu sitio web?</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño web] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>Tu sitio es parte de un sistema: UX/UI Design, E-commerce, SEO, CRO y Analítica de datos pueden trabajar conectados con el diseño web para que cada decisión tenga contexto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>SEO para que tu marca aparezca cuando importa | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>Combinamos estrategia SEO, contenido, arquitectura web, optimización técnica, autoridad y análisis para construir crecimiento orgánico sostenible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>SEO para que tu marca aparezca cuando importa | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>Combinamos estrategia SEO, contenido, arquitectura web, optimización técnica, autoridad y análisis para construir crecimiento orgánico sostenible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Datos Google (Service): name</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>SEO y posicionamiento en buscadores</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>SEO, SEO local y GEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Datos Google (Service): description</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Combinamos estrategia SEO, contenido, arquitectura web, optimización técnica, autoridad y análisis para construir crecimiento orgánico sostenible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué diferencia hay entre SEO y GEO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>El SEO posiciona tu sitio en buscadores como Google. El GEO prepara tu contenido para que herramientas de IA como ChatGPT, Perplexity o Google AI Overviews lo entiendan y lo usen como fuente. Ambos necesitan contenido, estructura y autoridad sólidos, por eso los trabajamos como disciplinas relacionadas, no como mundos separados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuánto tiempo toma ver resultados de SEO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>No hay un plazo universal: depende del estado de tu sitio, la competencia y la autoridad del dominio. En general, los primeros movimientos se ven entre 1 y 3 meses y los resultados más sólidos a partir del cuarto a sexto mes. Por eso empezamos con una línea base y medimos qué señales muestran que avanzamos hacia el resultado de negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>¿Trabajan SEO local para negocios con ubicación física?</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>Sí. Optimizamos tu perfil de Google Business y tu presencia local para que aparezcas en búsquedas de tu zona y en el mapa de Google.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>¿El SEO incluye la creación de contenido?</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Sí, la estrategia de contenido (blog, páginas de servicio, landing pages por intención de búsqueda) es parte central de cómo trabajamos SEO, no solo ajustes técnicos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué servicios se conectan con SEO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>[SEO] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Diseño web, GEO, SEO local, CRO y Analítica de datos. Lo que optimizamos genera datos, los datos generan preguntas, y las preguntas nos muestran qué debemos optimizar después.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>SEO Local y Google Business Profile | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Optimizamos tu perfil de Google Business y tu presencia local para que te encuentren cuando buscan tu servicio cerca, en el mapa y en resultados locales de Google.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>SEO Local y Google Business Profile | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Optimizamos tu perfil de Google Business y tu presencia local para que te encuentren cuando buscan tu servicio cerca, en el mapa y en resultados locales de Google.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Datos Google (Service): name</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>SEO local y Google Business Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>SEO local, optimización de Google Business Profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Datos Google (Service): description</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Optimizamos tu perfil de Google Business y tu presencia local para que te encuentren cuando buscan tu servicio cerca, en el mapa y en resultados locales de Google.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué negocios necesitan SEO local?</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Cualquier negocio con ubicación física o zona de servicio definida: clínicas, restaurantes, tiendas, oficinas profesionales: todo negocio donde 'cerca de mí' es una búsqueda relevante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué incluye la optimización de Google Business Profile?</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Configuración completa del perfil (categorías, horarios, fotos, descripción), gestión de reseñas y publicaciones periódicas para mantenerlo activo ante Google.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>¿El SEO local reemplaza al SEO general del sitio?</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>No, lo complementa. El SEO local se enfoca en búsquedas con intención geográfica; el SEO general sigue trabajando el resto de las búsquedas relevantes para tu negocio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuánto tiempo toma ver resultados en el mapa de Google?</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Suele ser más rápido que el SEO orgánico general: las primeras mejoras en el paquete local (mapa) de Google pueden verse en semanas, dependiendo de la competencia local.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué otros servicios se conectan con SEO local?</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>[SEO local] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>SEO, Diseño web y Analítica de datos: un perfil local optimizado funciona mejor cuando el sitio y la medición también están bien resueltos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>GEO: Posicionamiento para Motores de IA | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>GEO (Generative Engine Optimization): preparamos tu marca para ser comprendida, considerada y mencionada en respuestas de ChatGPT, Perplexity y Google AI Overviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>GEO: Posicionamiento para Motores de IA | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>GEO (Generative Engine Optimization): preparamos tu marca para ser comprendida, considerada y mencionada en respuestas de ChatGPT, Perplexity y Google AI Overviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Datos Google (Service): name</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>GEO (Generative Engine Optimization)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>GEO, posicionamiento en motores de IA generativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Datos Google (Service): description</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>GEO (Generative Engine Optimization): preparamos tu marca para ser comprendida, considerada y mencionada en respuestas de ChatGPT, Perplexity y Google AI Overviews.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>¿Cómo se mide el avance en GEO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Revisamos cómo responden los principales asistentes de IA a las preguntas clave de tu categoría, si mencionan tu marca y qué fuentes citan, junto con las métricas de SEO. GEO todavía está evolucionando, así que documentamos cada aprendizaje.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuál es la diferencia entre SEO y GEO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>El SEO busca mejorar la visibilidad en motores de búsqueda. El GEO busca preparar la marca para experiencias de búsqueda y respuesta generativa. No son enemigos: son capas diferentes de una misma evolución digital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>¿Puede una marca aparecer en ChatGPT o Google AI Overviews?</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Puede ser mencionada o utilizada como fuente dependiendo de la consulta, el sistema y las señales disponibles, pero ninguna agencia puede garantizar una posición o mención determinada. Lo que sí puede hacer una marca es construir una presencia digital clara, relevante, útil y respaldada por señales de autoridad. La optimización para IA no reemplaza el SEO tradicional: lo amplía.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>¿Para quién tiene sentido GEO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>GEO puede ser especialmente interesante para marcas que compiten en categorías con alta investigación, venden servicios especializados, tienen conocimiento propio que pueden convertir en contenido, quieren fortalecer su autoridad digital, ya cuentan con una base SEO, o quieren entender cómo está cambiando el descubrimiento de marcas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué otros servicios necesita una estrategia GEO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>[GEO posicionamiento IA] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>SEO, Diseño web, Analítica de datos y CRO. El objetivo no es aparecer por aparecer: es que exista suficiente contexto digital para que la marca pueda ser comprendida y considerada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>Pauta Digital y SEM (Meta, Google, TikTok) | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>Campañas de pauta digital en Meta, Google y TikTok con estrategia de segmentación, mensajes coordinados y piezas gráficas propias para cada plataforma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Pauta Digital y SEM (Meta, Google, TikTok) | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Campañas de pauta digital en Meta, Google y TikTok con estrategia de segmentación, mensajes coordinados y piezas gráficas propias para cada plataforma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Datos Google (Service): name</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Pauta digital y SEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>SEM, pauta digital, publicidad en Meta, Google y TikTok</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Datos Google (Service): description</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Campañas de pauta digital en Meta, Google y TikTok con estrategia de segmentación, mensajes coordinados y piezas gráficas propias para cada plataforma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>¿En qué plataformas de pauta trabajan?</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Meta Ads (Facebook e Instagram), Google Ads y TikTok Ads, eligiendo la combinación de plataformas según dónde esté tu audiencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>¿Necesito un presupuesto mínimo de pauta para empezar?</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>El presupuesto de pauta se define según tu objetivo y tu mercado; te ayudamos a definir un monto realista para obtener datos útiles desde las primeras semanas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>¿Incluyen el diseño de las piezas gráficas para las campañas?</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Sí, las piezas gráficas de las campañas las diseñamos con nuestro servicio de Diseño gráfico, coordinadas con el mensaje de la campaña.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>¿Cómo miden el resultado de una campaña de pauta?</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>Con la analítica y el tracking de conversiones configurado desde el inicio (GA4, píxeles y eventos), para saber qué campañas generan leads o ventas reales, no solo clics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>¿Por qué la pauta no debería quedar aislada?</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>El SEO y la pauta traen tráfico; el diseño y la creatividad ayudan a que ese tráfico entienda la oferta; el CRO ayuda a convertirlo; la analítica muestra qué está pasando. Coordinar esas piezas es lo que hace que una campaña funcione, no solo que exista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué otros servicios se conectan con pauta digital?</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>[Pauta digital] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>Diseño gráfico, CRO, Diseño web (para las landing pages) y Analítica de datos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>E-commerce diseñado para vender | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Diseñamos experiencias de e-commerce conectando estrategia, UX/UI, tecnología, SEO, conversión y analítica. No solo para exhibir productos: para venderlos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>E-commerce diseñado para vender | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Diseñamos experiencias de e-commerce conectando estrategia, UX/UI, tecnología, SEO, conversión y analítica. No solo para exhibir productos: para venderlos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Datos Google (Service): name</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>Diseño y desarrollo de e-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>E-commerce, tiendas en línea</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Datos Google (Service): description</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>Diseñamos experiencias de e-commerce conectando estrategia, UX/UI, tecnología, SEO, conversión y analítica. No solo para exhibir productos: para venderlos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué necesito tener listo para empezar?</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Tu catálogo (productos, precios, fotos y descripciones), las condiciones de envío y el medio de pago que quieres usar. Si algo de eso no está definido, lo trabajamos contigo como parte del proyecto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>¿El e-commerce incluye pasarela de pagos y checkout?</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>Sí, integramos la pasarela de pagos que mejor se ajuste a tu país y tu negocio, y trabajamos el checkout para reducir fricciones innecesarias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuánto tiempo toma desarrollar una tienda en línea?</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>Suele tomar entre 6 y 10 semanas, según el tamaño del catálogo y las integraciones necesarias (inventario, envíos, facturación). Te damos un cronograma concreto una vez definimos el alcance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>¿Por qué conectar e-commerce con SEO y CRO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>[Ecommerce] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>Porque atraer personas a una tienda es solo una parte del trabajo. El SEO puede ayudar a generar descubrimiento. La experiencia ayuda a que encuentren y entiendan. El CRO ayuda a reducir fricciones. La analítica muestra qué está pasando. El sistema completo es más poderoso que cualquiera de sus piezas aisladas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>UX/UI Design para experiencias digitales que funcionan | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>Diseñamos cómo las personas entienden y usan tu marca: arquitectura, flujos, wireframes, interfaz y prototipos, conectados con conversión y SEO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>UX/UI Design para experiencias digitales que funcionan | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Diseñamos cómo las personas entienden y usan tu marca: arquitectura, flujos, wireframes, interfaz y prototipos, conectados con conversión y SEO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Datos Google (Service): name</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>UX/UI Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Diseño de experiencia de usuario e interfaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Datos Google (Service): description</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Diseñamos cómo las personas entienden y usan tu marca: arquitectura, flujos, wireframes, interfaz y prototipos, conectados con conversión y SEO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué entregan al final de un proyecto de UX/UI?</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Según el alcance: arquitectura de información, flujos de usuario, wireframes, prototipos navegables y el diseño final de las interfaces, listos para que tu equipo o el nuestro los desarrolle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>¿El UX/UI Design es un servicio aparte o va incluido en el diseño web?</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>El UX/UI es parte del proceso de diseño web y e-commerce, pero también lo ofrecemos como servicio independiente para productos digitales, apps o rediseños de interfaz sin tocar el desarrollo completo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuánto cuesta un proyecto de UX/UI?</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Depende de cuántas pantallas y recorridos hay que diseñar y de si incluye prototipos o un design system. Cuéntanos tu proyecto y te compartimos una propuesta ajustada a tu alcance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuándo necesitas UX/UI?</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>Cuando tienes una web difícil de usar. Cuando tu producto digital creció sin una estructura clara. Cuando estás rediseñando una experiencia. Cuando tienes tráfico pero los usuarios no avanzan. O cuando sabes que algo no funciona, pero todavía no sabes exactamente qué.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>¿Por qué UX/UI también afecta el SEO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>Porque una experiencia clara ayuda a las personas a encontrar, comprender y consumir información. Además, la arquitectura de contenido y navegación puede ayudar a que los motores entiendan mejor la relación entre las páginas. SEO y UX no deberían diseñarse en habitaciones separadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué otros servicios se conectan con UX/UI?</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>[UX-UI design] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Diseño web, E-commerce, CRO y SEO: cuando la experiencia, la conversión y la búsqueda se piensan juntas, cada decisión tiene más contexto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>Diseño Gráfico Digital: Piezas para Redes y Marca | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Piezas gráficas para redes, presentaciones y material digital, con la misma estética de tu sitio y tu marca en todos los canales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>Diseño Gráfico Digital: Piezas para Redes y Marca | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>Piezas gráficas para redes, presentaciones y material digital, con la misma estética de tu sitio y tu marca en todos los canales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Datos Google (Service): name</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>Diseño gráfico digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Diseño gráfico, piezas para redes sociales y presentaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Datos Google (Service): description</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Piezas gráficas para redes, presentaciones y material digital, con la misma estética de tu sitio y tu marca en todos los canales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué tipo de piezas gráficas diseñan?</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Posts y carruseles para redes sociales, presentaciones corporativas, material para pauta digital, y piezas de apoyo para campañas o lanzamientos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>¿El diseño gráfico mantiene coherencia con mi sitio web?</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>Sí, es justamente el objetivo: que cada pieza (red social, presentación, anuncio) se sienta parte de la misma marca que ve tu sitio web.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>¿Pueden diseñar solo piezas puntuales, sin un proyecto grande?</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>Sí, trabajamos tanto paquetes recurrentes de contenido para redes como piezas puntuales para una campaña o lanzamiento específico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>¿Incluye definir la identidad de marca (logo, colores)?</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>[Diseño gráfico] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>Si tu marca aún no tiene una identidad definida, podemos construirla como parte del proyecto; si ya la tienes, diseñamos sobre esa base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>CRO: convierte mejor el tráfico que ya tienes | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>CRO (Conversion Rate Optimization): analizamos y mejoramos tu experiencia digital para aumentar la probabilidad de que los usuarios completen una acción importante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>CRO: convierte mejor el tráfico que ya tienes | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>CRO (Conversion Rate Optimization): analizamos y mejoramos tu experiencia digital para aumentar la probabilidad de que los usuarios completen una acción importante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Datos Google (Service): name</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>CRO (Optimización de la Tasa de Conversión)</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>CRO, optimización de conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Datos Google (Service): description</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>CRO (Conversion Rate Optimization): analizamos y mejoramos tu experiencia digital para aumentar la probabilidad de que los usuarios completen una acción importante.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuánto cuesta un proyecto de CRO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>Depende del tamaño del sitio y de cuántas páginas o recorridos vamos a analizar. Empezamos con un diagnóstico y, a partir de lo que encontremos, te proponemos un plan de mejoras ajustado a tu presupuesto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué necesito para empezar con CRO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>Idealmente, un sitio que ya recibe visitas y una analítica que mida las conversiones. Si todavía no mides bien, empezamos por configurar el tracking: sin datos confiables no hay forma de saber si una mejora funcionó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>¿Cómo se conecta CRO con SEO y pauta?</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>SEO y pauta ayudan a traer personas. CRO ayuda a mejorar lo que ocurre después. Analítica permite entender el comportamiento. Tráfico → Experiencia → Conversión → Datos → Optimización: ese ciclo es parte de la forma en que entendemos el crecimiento en WOW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>¿Cuándo necesitas CRO?</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>[CRO] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>Si tienes tráfico pero pocas conversiones. Si inviertes en pauta y el costo por oportunidad es demasiado alto. Si tu SEO está creciendo pero las conversiones no acompañan. O si simplemente quieres dejar de tomar decisiones de diseño basadas únicamente en opiniones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t>Analítica de Datos, Reportería y Dashboards | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t>Configuramos GA4, Tag Manager y eventos de conversión, y traducimos el comportamiento de tu audiencia en dashboards y decisiones claras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t>Analítica de Datos, Reportería y Dashboards | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t>Configuramos GA4, Tag Manager y eventos de conversión, y traducimos el comportamiento de tu audiencia en dashboards y decisiones claras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Datos Google (Service): name</t>
+        </is>
+      </c>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t>Analítica de datos, reportería y dashboards</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t>Analítica web, configuración de tracking, reportería</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Datos Google (Service): description</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>Configuramos GA4, Tag Manager y eventos de conversión, y traducimos el comportamiento de tu audiencia en dashboards y decisiones claras.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué incluye la configuración de analítica y tracking?</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>Configuración de Google Analytics 4, Google Tag Manager y los eventos de conversión específicos de tu sitio (formularios, compras, clics en WhatsApp, etc.): la base técnica sin la que no hay datos confiables que analizar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>¿Puedo tener un dashboard sin depender de hojas de cálculo?</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>Sí, construimos dashboards que centralizan tus métricas clave en un solo lugar, actualizados automáticamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>¿La analítica sirve solo para SEO y pauta digital?</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>No, también sirve para entender comportamiento de usuario en el sitio, identificar puntos de fuga en el embudo de conversión y priorizar qué optimizar primero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>¿Cada cuánto recibo reportes?</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>[Analítica de datos] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>Lo definimos contigo según el ritmo de tu negocio: los dashboards se actualizan solos y los acompañamos con revisiones periódicas para convertir los datos en decisiones. Si antes necesitas definir qué medir, está nuestra consultoría de datos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>Configuración de Analítica y Tracking (GA4, Tag Manager) | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>Configuramos GA4, Google Tag Manager y eventos de conversión: la base técnica sin la que no hay datos confiables que analizar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>Configuración de Analítica y Tracking (GA4, Tag Manager) | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>Configuramos GA4, Google Tag Manager y eventos de conversión: la base técnica sin la que no hay datos confiables que analizar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Datos Google (Service): name</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>Configuración de analítica y tracking</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>Configuración de GA4, Google Tag Manager y eventos de conversión</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Datos Google (Service): description</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>Configuramos GA4, Google Tag Manager y eventos de conversión: la base técnica sin la que no hay datos confiables que analizar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>¿Por qué necesito configurar bien GA4 y Tag Manager desde el inicio?</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>Sin una configuración correcta, los datos que ves (tráfico, conversiones, comportamiento) pueden estar incompletos o ser directamente incorrectos, lo que lleva a decisiones equivocadas de SEO, pauta o producto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué eventos de conversión configuran?</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>Los específicos de tu negocio: envíos de formulario, clics en WhatsApp o llamada, compras, agregar al carrito, descargas: cualquier acción que consideres una conversión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>¿Esto reemplaza el servicio de analítica de datos?</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>No, es la base técnica sobre la que se apoya. Una vez configurado el tracking, el servicio de analítica y reportería usa esos datos para generar dashboards y recomendaciones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>¿También configuran el consentimiento de cookies?</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>[Config analítica y tracking] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>Sí, incluimos la configuración de consentimiento necesaria para operar el tracking de forma correcta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>Consultoría de Datos: Qué Medir y Por Qué | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>Te ayudamos a decidir qué medir y por qué, alineando la analítica con los objetivos reales de tu negocio, no solo entregando un dashboard más.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>Consultoría de Datos: Qué Medir y Por Qué | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>Te ayudamos a decidir qué medir y por qué, alineando la analítica con los objetivos reales de tu negocio, no solo entregando un dashboard más.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Datos Google (Service): name</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t>Consultoría de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>Consultoría de analítica y datos de negocio</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Datos Google (Service): description</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>Te ayudamos a decidir qué medir y por qué, alineando la analítica con los objetivos reales de tu negocio, no solo entregando un dashboard más.</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>¿En qué se diferencia de la configuración de analítica?</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>La configuración de tracking y los dashboards son la parte técnica; la consultoría de datos es la capa de criterio: qué métricas importan para tus objetivos de negocio y cómo interpretarlas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>¿Para qué tipo de negocios tiene sentido esta consultoría?</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>Para negocios que ya tienen datos (de sitio, ventas o pauta) pero no tienen claro qué priorizar, o que quieren definir una estrategia de medición antes de invertir en más herramientas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>¿Es un servicio puntual o continuo?</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>Puede ser ambos: una consultoría inicial para definir qué medir y cómo, o un acompañamiento periódico que revisa datos y ajusta prioridades con el tiempo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué recibo al final de la consultoría?</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>[Consultoría de datos] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>Un documento con las métricas que importan para tu negocio, qué medir y cómo, qué dejar de medir, y las decisiones prioritarias que se desprenden de tus datos actuales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>Ruta</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>Cursos Digitales de SEO, Pauta y Analítica | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>Talleres y cursos para que tu equipo maneje SEO, pauta digital y analítica de datos por su cuenta, con criterio propio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>Cursos Digitales de SEO, Pauta y Analítica | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>Talleres y cursos para que tu equipo maneje SEO, pauta digital y analítica de datos por su cuenta, con criterio propio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Datos Google (Service): name</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>Cursos digitales</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>Formación y talleres en marketing digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Datos Google (Service): description</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>Talleres y cursos para que tu equipo maneje SEO, pauta digital y analítica de datos por su cuenta, con criterio propio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué temas cubren los cursos digitales?</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>SEO, pauta digital (Meta, Google, TikTok Ads) y analítica de datos (GA4, dashboards), adaptados al nivel y las herramientas que ya usa tu equipo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>¿Los cursos son para principiantes o para equipos con experiencia?</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>Ajustamos el contenido según el punto de partida del equipo: desde fundamentos para quien empieza, hasta profundización en herramientas específicas para equipos con experiencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>¿Se dictan de forma presencial o virtual?</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>Trabajamos 100% remoto, así que los talleres se dictan por videollamada, con materiales y ejercicios prácticos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Datos Google: FAQ pregunta</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>¿Hay un temario fijo o se adapta a mi equipo?</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>[Cursos digitales] Datos Google: FAQ respuesta</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>Ambas opciones existen: un taller estructurado con temario definido, o un acompañamiento más flexible según lo que tu equipo necesite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Brand Experience] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: Diseño web</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Brand Experience] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: UX/UI Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Brand Experience] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: E-commerce</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Brand Experience] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: Diseño gráfico</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Brand Experience] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Brand Experience] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Brand Experience] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>Brand &amp; Experience Lab: Diseño Web y UX/UI | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Brand Experience] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>Brand &amp; Experience Lab convierte objetivos de negocio en un sitio real: diseño web, UX/UI, e-commerce y diseño gráfico, con dirección de marca desde el primer boceto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Brand Experience] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Brand Experience] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>Brand &amp; Experience Lab: Diseño Web y UX/UI | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Brand Experience] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>Brand &amp; Experience Lab convierte objetivos de negocio en un sitio real: diseño web, UX/UI, e-commerce y diseño gráfico, con dirección de marca desde el primer boceto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Brand Experience] Datos Google (Service): name</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Brand Experience] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>Diseño web, UX/UI, e-commerce y diseño gráfico</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Brand Experience] Datos Google (Service): description</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>Brand &amp; Experience Lab convierte objetivos de negocio en un sitio real: diseño web, UX/UI, e-commerce y diseño gráfico, con dirección de marca desde el primer boceto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: SEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: SEO local &amp; GBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: GEO (posicionamiento en IA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: CRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: Pauta digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: Analítica de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: Configuración de analítica</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: Consultoría de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>Ver más: Cursos digitales</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Texto de accesibilidad (aria-label)</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Meta og:site_name</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>Insight Lab: SEO, SEM y Analítica de Datos | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>Insight Lab lleva tu marca a las personas correctas y mide lo que realmente funciona: SEO, GEO, pauta digital, CRO y analítica de datos convertidos en decisiones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Meta og:image:alt</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Meta twitter:title</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>Insight Lab: SEO, SEM y Analítica de Datos | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Meta twitter:description</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>Insight Lab lleva tu marca a las personas correctas y mide lo que realmente funciona: SEO, GEO, pauta digital, CRO y analítica de datos convertidos en decisiones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Datos Google (Service): name</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>Insight Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Datos Google (Service): serviceType</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>SEO, SEM, GEO, CRO y analítica de datos</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>[Lab Insight] Datos Google (Service): description</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>Insight Lab lleva tu marca a las personas correctas y mide lo que realmente funciona: SEO, GEO, pauta digital, CRO y analítica de datos convertidos en decisiones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>[Pronto] Meta og:title</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>Muy pronto | Workshop of Wonders</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>[Pronto] Meta og:description</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>Estamos construyendo algo maravilloso. Muy pronto abrimos las puertas del taller.</t>
         </is>
       </c>
     </row>
@@ -23174,7 +27615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -23201,7 +27642,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Orbit</t>
+          <t>Lámparas Milán</t>
         </is>
       </c>
     </row>
@@ -23213,7 +27654,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Moda · Ropa deportiva</t>
+          <t>Iluminación · Hogar y decoración</t>
         </is>
       </c>
     </row>
@@ -23225,7 +27666,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>*Orbita* tu pasión</t>
+          <t>Fabrica *bellezas*</t>
         </is>
       </c>
     </row>
@@ -23237,7 +27678,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Marca de ropa deportiva de Centroamérica.</t>
+          <t>Empresa de iluminación y decoración para el hogar.</t>
         </is>
       </c>
     </row>
@@ -23249,7 +27690,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Naming, logo y sistema de color construidos desde cero para posicionar a Orbit como marca de ropa deportiva en Centroamérica.</t>
+          <t>Refresh y rebranding de una marca existente, manteniendo sus valores y esencia. Diseño y desarrollo del sitio web, estrategia de marketing digital, pauta digital y SEO.</t>
         </is>
       </c>
     </row>
@@ -23261,7 +27702,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+          <t>Identidad y diseño de marca · Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
         </is>
       </c>
     </row>
@@ -23273,7 +27714,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>De cero a órbita.</t>
+          <t>Le cambiamos la luz, no la esencia.</t>
         </is>
       </c>
     </row>
@@ -23285,7 +27726,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Orbit quería entrar al mercado de ropa deportiva en Centroamérica sin nada construido (ni nombre, ni logo, ni colores) y competir con marcas ya conocidas.</t>
+          <t>Lámparas Milán ya tenía clientes y una marca reconocida, pero su imagen necesitaba ponerse al día y su presencia digital tenía que empezar a trabajar para vender. El reto: modernizarla sin perder lo que la hacía reconocible.</t>
         </is>
       </c>
     </row>
@@ -23297,7 +27738,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>En ropa deportiva la gente compra identidad: quiere sentirse parte de algo cuando entrena.</t>
+          <t>Sus clientes no compran solo una lámpara: compran cómo se va a ver su casa. La marca tenía que mostrar espacios, no solo productos.</t>
         </is>
       </c>
     </row>
@@ -23309,7 +27750,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Un nombre que habla de movimiento y constancia, un logo pensado para vivir en las prendas y un sistema de color con energía deportiva.</t>
+          <t>Un refresh de marca que conserva su esencia con una imagen más actual; un sitio web donde los productos se ven en ambientes reales; y una estrategia de SEO y pauta digital para llegar a quienes están decorando o remodelando su hogar.</t>
         </is>
       </c>
     </row>
@@ -23321,31 +27762,139 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cuando se parte de cero, el nombre y el color son la primera promesa de la marca.</t>
+          <t>Renovar no es empezar de cero: lo que la gente ya reconoce de una marca es un activo que hay que cuidar.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Herramientas</t>
+          <t>Botón "Ver sitio" (enlace)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Adobe Illustrator</t>
+          <t>https://www.cristaleriamilan.com/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Wix, Adobe Illustrator, Semrush, Search Console, Google Analytics 4, Google My Business, Google Ads, Meta Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t>Capacidades — Brand &amp; Experience Lab</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Naming, Logo, Sistema de color</t>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Rebranding, Diseño web, Desarrollo web</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Insight Lab</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marketing digital, Pauta digital, SEO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Maroon · #52000D</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Peru · #C69538</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Dim Gray · #505858</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Lavender · #DEE9EB</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Light Gray · #E3D5CC</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "Aa"</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Coustard</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "123"</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Coustard</t>
         </is>
       </c>
     </row>
@@ -25310,7 +29859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -25337,7 +29886,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Ajá Waffles</t>
+          <t>Orbit</t>
         </is>
       </c>
     </row>
@@ -25349,7 +29898,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Gastronomía</t>
+          <t>Moda · Ropa deportiva</t>
         </is>
       </c>
     </row>
@@ -25361,7 +29910,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>El sabor de la costa *en cada bocado*</t>
+          <t>*Orbita* tu pasión</t>
         </is>
       </c>
     </row>
@@ -25373,7 +29922,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Emprendimiento de waffles a base de yuca.</t>
+          <t>Marca de ropa deportiva de Centroamérica.</t>
         </is>
       </c>
     </row>
@@ -25385,7 +29934,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Ajá Waffles es un emprendimiento gastronómico nuevo con un diferencial claro: waffles a base de yuca. Necesitaban una marca desde cero que reflejara ese sabor costeño y se destacara frente a las cafeterías tradicionales. Construimos el naming, la propuesta de valor, el logo, los colores y la identidad visual, y diseñamos la estrategia de marketing digital para su lanzamiento.</t>
+          <t>Naming, logo y sistema de color construidos desde cero para posicionar a Orbit como marca de ropa deportiva en Centroamérica.</t>
         </is>
       </c>
     </row>
@@ -25397,7 +29946,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de marca · Identidad y diseño de marca · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
         </is>
       </c>
     </row>
@@ -25409,7 +29958,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>¿Waffles de yuca? ¡Ajá, eso!</t>
+          <t>De cero a órbita.</t>
         </is>
       </c>
     </row>
@@ -25421,7 +29970,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Ajá Waffles es un emprendimiento gastronómico nuevo con un diferencial claro: waffles a base de yuca. Sin marca ni presencia digital todavía, competía por atención frente a cafeterías ya conocidas.</t>
+          <t>Orbit quería entrar al mercado de ropa deportiva en Centroamérica sin nada construido (ni nombre, ni logo, ni colores) y competir con marcas ya conocidas.</t>
         </is>
       </c>
     </row>
@@ -25433,7 +29982,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Su público no buscaba una cafetería más: buscaba algo distinto a las cafeterías tradicionales.</t>
+          <t>En ropa deportiva la gente compra identidad: quiere sentirse parte de algo cuando entrena.</t>
         </is>
       </c>
     </row>
@@ -25445,7 +29994,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Una estrategia de lanzamiento centrada en su diferencial (waffles de yuca con el sabor de la costa): un mensaje que lo pone en primer plano desde el primer contacto y contenidos pensados para despertar curiosidad en quienes buscan algo distinto a la cafetería de siempre.</t>
+          <t>Un nombre que habla de movimiento y constancia, un logo pensado para vivir en las prendas y un sistema de color con energía deportiva.</t>
         </is>
       </c>
     </row>
@@ -25457,7 +30006,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Un producto diferente necesita un mensaje igual de distinto para encontrar a quien lo estaba buscando.</t>
+          <t>Cuando se parte de cero, el nombre y el color son la primera promesa de la marca.</t>
         </is>
       </c>
     </row>
@@ -25469,19 +30018,91 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Canva, Adobe Illustrator</t>
+          <t>Adobe Illustrator</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Capacidades — Insight Lab</t>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de marketing digital, Estrategia de lanzamiento</t>
+          <t>Naming, Logo, Sistema de color</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Black · #000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Lavender · #DEE9EB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Dim Gray · #505858</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Dim Gray · #73616F</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "Aa"</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Teko</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "123"</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Teko</t>
         </is>
       </c>
     </row>
@@ -25496,7 +30117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -25523,7 +30144,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Arlo</t>
+          <t>Ajá Waffles</t>
         </is>
       </c>
     </row>
@@ -25535,7 +30156,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Legal · Industrias creativas</t>
+          <t>Gastronomía</t>
         </is>
       </c>
     </row>
@@ -25547,7 +30168,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Para lo legal, un poco de *creatividad*</t>
+          <t>El sabor de la costa *en cada bocado*</t>
         </is>
       </c>
     </row>
@@ -25559,7 +30180,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Firma de abogados especializada en servicios legales para creativos.</t>
+          <t>Emprendimiento de waffles a base de yuca.</t>
         </is>
       </c>
     </row>
@@ -25571,7 +30192,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Definición de propuesta de valor y desarrollo de identidad visual. Organización del sistema de marca, selección de colores y construcción de Brand Book. El proyecto no incluyó el diseño del logo ni de la mascota Arlo.</t>
+          <t>Ajá Waffles es un emprendimiento gastronómico nuevo con un diferencial claro: waffles a base de yuca. Necesitaban una marca desde cero que reflejara ese sabor costeño y se destacara frente a las cafeterías tradicionales. Construimos el naming, la propuesta de valor, el logo, los colores y la identidad visual, y diseñamos la estrategia de marketing digital para su lanzamiento.</t>
         </is>
       </c>
     </row>
@@ -25583,7 +30204,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+          <t>Estrategia de marca · Identidad y diseño de marca · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
         </is>
       </c>
     </row>
@@ -25595,7 +30216,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Abogados que hablan creativo.</t>
+          <t>¿Waffles de yuca? ¡Ajá, eso!</t>
         </is>
       </c>
     </row>
@@ -25607,7 +30228,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Arlo es una firma de abogados para creativos. Ya tenía logo y mascota, pero le faltaba una propuesta de valor clara y un sistema de marca que la hiciera coherente.</t>
+          <t>Ajá Waffles es un emprendimiento gastronómico nuevo con un diferencial claro: waffles a base de yuca. Sin marca ni presencia digital todavía, competía por atención frente a cafeterías ya conocidas.</t>
         </is>
       </c>
     </row>
@@ -25619,7 +30240,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Los creativos suelen ver lo legal como algo frío y lejano; la marca tenía que sentirse cercana a su mundo.</t>
+          <t>Su público no buscaba una cafetería más: buscaba algo distinto a las cafeterías tradicionales.</t>
         </is>
       </c>
     </row>
@@ -25631,7 +30252,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Definimos su propuesta de valor, organizamos su sistema de marca, seleccionamos la paleta de color y construimos un Brand Book para que la marca se use igual en todas partes.</t>
+          <t>Una estrategia de lanzamiento centrada en su diferencial (waffles de yuca con el sabor de la costa): un mensaje que lo pone en primer plano desde el primer contacto y contenidos pensados para despertar curiosidad en quienes buscan algo distinto a la cafetería de siempre.</t>
         </is>
       </c>
     </row>
@@ -25643,7 +30264,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Ordenar un sistema de marca también es diseño: a veces el trabajo es darle estructura a lo que ya existe.</t>
+          <t>Un producto diferente necesita un mensaje igual de distinto para encontrar a quien lo estaba buscando.</t>
         </is>
       </c>
     </row>
@@ -25655,19 +30276,91 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Adobe Illustrator</t>
+          <t>Canva, Adobe Illustrator</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
+          <t>Capacidades — Insight Lab</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Propuesta de valor, Identidad visual, Sistema de marca, Brand Book</t>
+          <t>Estrategia de marketing digital, Estrategia de lanzamiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Light Sea Green · #01B6A6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Gold · #FDD924</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Chocolate · #D95C00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Papaya Whip · #FFEFDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "Aa"</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Fredoka</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "123"</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Fredoka</t>
         </is>
       </c>
     </row>
@@ -25682,7 +30375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -25709,7 +30402,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Tin-T!</t>
+          <t>Arlo</t>
         </is>
       </c>
     </row>
@@ -25721,7 +30414,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Merchandising · Diseño colombiano</t>
+          <t>Legal · Industrias creativas</t>
         </is>
       </c>
     </row>
@@ -25733,7 +30426,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Recuerdos que *cuentan historias*</t>
+          <t>Para lo legal, un poco de *creatividad*</t>
         </is>
       </c>
     </row>
@@ -25745,7 +30438,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Emprendimiento colombiano de merchandising.</t>
+          <t>Firma de abogados especializada en servicios legales para creativos.</t>
         </is>
       </c>
     </row>
@@ -25757,7 +30450,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Desarrollo de la marca, incluyendo propuesta de valor e identidad visual. Creación de los personajes Cafecito y Aguacatico, concebidos como parte del universo de la marca y desarrollados para merchandising y diferentes aplicaciones.</t>
+          <t>Definición de propuesta de valor y desarrollo de identidad visual. Organización del sistema de marca, selección de colores y construcción de Brand Book. El proyecto no incluyó el diseño del logo ni de la mascota Arlo.</t>
         </is>
       </c>
     </row>
@@ -25781,7 +30474,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Cafecito, Aguacatico y una marca con personalidad.</t>
+          <t>Abogados que hablan creativo.</t>
         </is>
       </c>
     </row>
@@ -25793,7 +30486,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Tin-T! es un emprendimiento colombiano de merchandising. En un mercado lleno de recuerdos parecidos, necesitaba una marca que se quedara en la memoria.</t>
+          <t>Arlo es una firma de abogados para creativos. Ya tenía logo y mascota, pero le faltaba una propuesta de valor clara y un sistema de marca que la hiciera coherente.</t>
         </is>
       </c>
     </row>
@@ -25805,7 +30498,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Un recuerdo se compra por la historia que cuenta, no por el objeto.</t>
+          <t>Los creativos suelen ver lo legal como algo frío y lejano; la marca tenía que sentirse cercana a su mundo.</t>
         </is>
       </c>
     </row>
@@ -25817,7 +30510,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Propuesta de valor, identidad visual y dos personajes, Cafecito y Aguacatico, inspirados en íconos colombianos, diseñados para vivir en productos y aplicaciones de la marca.</t>
+          <t>Definimos su propuesta de valor, organizamos su sistema de marca, seleccionamos la paleta de color y construimos un Brand Book para que la marca se use igual en todas partes.</t>
         </is>
       </c>
     </row>
@@ -25829,7 +30522,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Los personajes convierten un producto en un recuerdo.</t>
+          <t>Ordenar un sistema de marca también es diseño: a veces el trabajo es darle estructura a lo que ya existe.</t>
         </is>
       </c>
     </row>
@@ -25853,7 +30546,67 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Propuesta de valor, Identidad visual, Personajes, Merchandising</t>
+          <t>Propuesta de valor, Identidad visual, Sistema de marca, Brand Book</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Sandy Brown · #FBA35C</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Steel Blue · #528BBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Dark Slate Blue · #2A507D</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "Aa"</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Bree Serif</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "123"</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Bree Serif</t>
         </is>
       </c>
     </row>
@@ -25868,7 +30621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -25895,7 +30648,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Moosy</t>
+          <t>Tin-T!</t>
         </is>
       </c>
     </row>
@@ -25907,7 +30660,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Moda · Comercio</t>
+          <t>Merchandising · Diseño colombiano</t>
         </is>
       </c>
     </row>
@@ -25919,7 +30672,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Moda con *carácter propio*.</t>
+          <t>Recuerdos que *cuentan historias*</t>
         </is>
       </c>
     </row>
@@ -25931,7 +30684,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Tienda de moda.</t>
+          <t>Emprendimiento colombiano de merchandising.</t>
         </is>
       </c>
     </row>
@@ -25943,7 +30696,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Desarrollo de identidad visual para una tienda de moda con personalidad propia.</t>
+          <t>Desarrollo de la marca, incluyendo propuesta de valor e identidad visual. Creación de los personajes Cafecito y Aguacatico, concebidos como parte del universo de la marca y desarrollados para merchandising y diferentes aplicaciones.</t>
         </is>
       </c>
     </row>
@@ -25955,7 +30708,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
         </is>
       </c>
     </row>
@@ -25967,7 +30720,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Moda que no se viste igual.</t>
+          <t>Cafecito, Aguacatico y una marca con personalidad.</t>
         </is>
       </c>
     </row>
@@ -25979,7 +30732,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Moosy es una tienda de moda con personalidad propia, pero su imagen no lo estaba reflejando.</t>
+          <t>Tin-T! es un emprendimiento colombiano de merchandising. En un mercado lleno de recuerdos parecidos, necesitaba una marca que se quedara en la memoria.</t>
         </is>
       </c>
     </row>
@@ -25991,7 +30744,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>En moda, la identidad visual es lo primero que el cliente "se prueba".</t>
+          <t>Un recuerdo se compra por la historia que cuenta, no por el objeto.</t>
         </is>
       </c>
     </row>
@@ -26003,7 +30756,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Una identidad visual con carácter, pensada para destacar en redes y en la tienda.</t>
+          <t>Propuesta de valor, identidad visual y dos personajes, Cafecito y Aguacatico, inspirados en íconos colombianos, diseñados para vivir en productos y aplicaciones de la marca.</t>
         </is>
       </c>
     </row>
@@ -26015,7 +30768,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Una tienda con personalidad propia necesita una identidad que no se parezca a las demás.</t>
+          <t>Los personajes convierten un producto en un recuerdo.</t>
         </is>
       </c>
     </row>
@@ -26039,7 +30792,79 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Identidad visual</t>
+          <t>Propuesta de valor, Identidad visual, Personajes, Merchandising</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Light Sea Green · #20989D</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Crimson · #D0085C</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Goldenrod · #D0CD08</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Lime Green · #08D033</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Dim Gray · #505858</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Lavender · #DEE9EB</t>
         </is>
       </c>
     </row>
@@ -26081,7 +30906,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Indeleble</t>
+          <t>Moosy</t>
         </is>
       </c>
     </row>
@@ -26093,7 +30918,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Servicios profesionales · Contabilidad</t>
+          <t>Moda · Comercio</t>
         </is>
       </c>
     </row>
@@ -26105,7 +30930,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>La huella *indeleble* de tus finanzas</t>
+          <t>Moda con *carácter propio*.</t>
         </is>
       </c>
     </row>
@@ -26117,7 +30942,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Firma contable.</t>
+          <t>Tienda de moda.</t>
         </is>
       </c>
     </row>
@@ -26129,7 +30954,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>El punto de partida fue el nombre: le dimos identidad a esta firma contable con un sistema visual construido a partir de su naming.</t>
+          <t>Desarrollo de identidad visual para una tienda de moda con personalidad propia.</t>
         </is>
       </c>
     </row>
@@ -26141,7 +30966,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+          <t>Identidad y diseño de marca · Brand &amp; Experience Lab</t>
         </is>
       </c>
     </row>
@@ -26153,7 +30978,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Un nombre que deja huella, una marca que no se borra.</t>
+          <t>Moda que no se viste igual.</t>
         </is>
       </c>
     </row>
@@ -26165,7 +30990,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Indeleble, una firma contable, ya tenía un nombre con fuerza, pero no una identidad visual que lo respaldara en un sector que suele verse igual.</t>
+          <t>Moosy es una tienda de moda con personalidad propia, pero su imagen no lo estaba reflejando.</t>
         </is>
       </c>
     </row>
@@ -26177,7 +31002,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>El nombre ya contaba una historia: una huella que no se borra.</t>
+          <t>En moda, la identidad visual es lo primero que el cliente "se prueba".</t>
         </is>
       </c>
     </row>
@@ -26189,7 +31014,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Un sistema visual construido a partir del nombre: la idea de una huella que no se borra, traducida en logo, colores y aplicaciones.</t>
+          <t>Una identidad visual con carácter, pensada para destacar en redes y en la tienda.</t>
         </is>
       </c>
     </row>
@@ -26201,7 +31026,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cuando el nombre es fuerte, la identidad tiene que amplificarlo, no competir con él.</t>
+          <t>Una tienda con personalidad propia necesita una identidad que no se parezca a las demás.</t>
         </is>
       </c>
     </row>
@@ -26225,7 +31050,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Identidad visual, Sistema visual</t>
+          <t>Identidad visual</t>
         </is>
       </c>
     </row>
@@ -26240,7 +31065,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -26267,7 +31092,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Pretty Pets</t>
+          <t>Indeleble</t>
         </is>
       </c>
     </row>
@@ -26279,7 +31104,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Mascotas · Comercio</t>
+          <t>Servicios profesionales · Contabilidad</t>
         </is>
       </c>
     </row>
@@ -26291,7 +31116,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>*Pretty,* así como tu mascota</t>
+          <t>La huella *indeleble* de tus finanzas</t>
         </is>
       </c>
     </row>
@@ -26303,7 +31128,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Tienda de artículos para mascotas.</t>
+          <t>Firma contable.</t>
         </is>
       </c>
     </row>
@@ -26315,7 +31140,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Identidad de marca para una tienda de mascotas, acompañada de estrategia y pauta digital para llevar esa identidad a sus canales de venta.</t>
+          <t>El punto de partida fue el nombre: le dimos identidad a esta firma contable con un sistema visual construido a partir de su naming.</t>
         </is>
       </c>
     </row>
@@ -26327,7 +31152,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Identidad y diseño de marca · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
         </is>
       </c>
     </row>
@@ -26339,7 +31164,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Visitas que mueven la cola.</t>
+          <t>Un nombre que deja huella, una marca que no se borra.</t>
         </is>
       </c>
     </row>
@@ -26351,7 +31176,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Pretty Pets tenía productos y canales de venta, pero necesitaba que llegaran a ellos personas realmente interesadas en comprar para sus mascotas.</t>
+          <t>Indeleble, una firma contable, ya tenía un nombre con fuerza, pero no una identidad visual que lo respaldara en un sector que suele verse igual.</t>
         </is>
       </c>
     </row>
@@ -26363,7 +31188,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Quien compra para su mascota compra con el corazón, y lo hace en los canales donde ya confía.</t>
+          <t>El nombre ya contaba una historia: una huella que no se borra.</t>
         </is>
       </c>
     </row>
@@ -26375,7 +31200,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Una estrategia digital que parte de las mascotas y sus dueños, no del catálogo, y campañas de pauta segmentadas por intereses que llevan directo a sus canales de venta.</t>
+          <t>Un sistema visual construido a partir del nombre: la idea de una huella que no se borra, traducida en logo, colores y aplicaciones.</t>
         </is>
       </c>
     </row>
@@ -26387,7 +31212,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>La pauta rinde más cuando lleva a la gente a donde ya compra, no a un canal nuevo.</t>
+          <t>Cuando el nombre es fuerte, la identidad tiene que amplificarlo, no competir con él.</t>
         </is>
       </c>
     </row>
@@ -26399,19 +31224,67 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Meta Ads</t>
+          <t>Adobe Illustrator</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Capacidades — Insight Lab</t>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Estrategia digital, Pauta digital</t>
+          <t>Identidad visual, Sistema visual</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Dim Gray · #833C85</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Indigo · #4E1781</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "Aa"</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Bree Serif</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "123"</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Bree Serif</t>
         </is>
       </c>
     </row>
@@ -26426,7 +31299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -26453,7 +31326,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Prepapp</t>
+          <t>Pretty Pets</t>
         </is>
       </c>
     </row>
@@ -26465,7 +31338,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Educación · Tecnología</t>
+          <t>Mascotas · Comercio</t>
         </is>
       </c>
     </row>
@@ -26477,7 +31350,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Prepárate para la *siguiente etapa*</t>
+          <t>*Pretty,* así como tu mascota</t>
         </is>
       </c>
     </row>
@@ -26489,7 +31362,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Aplicación enfocada en la preparación para exámenes de Estado.</t>
+          <t>Tienda de artículos para mascotas.</t>
         </is>
       </c>
     </row>
@@ -26501,7 +31374,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Prepapp es una app enfocada en preparar estudiantes para exámenes de Estado. El reto no era solo la marca, sino construir un universo propio que la hiciera cercana a su público joven: naming, propuesta de valor, identidad visual, logo, colores y un sistema de personajes que le dieran personalidad a la app más allá de la funcionalidad.</t>
+          <t>Identidad de marca para una tienda de mascotas, acompañada de estrategia y pauta digital para llevar esa identidad a sus canales de venta.</t>
         </is>
       </c>
     </row>
@@ -26513,7 +31386,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+          <t>Identidad y diseño de marca · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
         </is>
       </c>
     </row>
@@ -26525,7 +31398,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Estudiar para el examen, pero con amigos.</t>
+          <t>Visitas que mueven la cola.</t>
         </is>
       </c>
     </row>
@@ -26537,7 +31410,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Prepapp es una app enfocada en preparar estudiantes para exámenes de Estado. El reto no era solo la marca, sino construir un universo propio que la hiciera cercana a su público joven.</t>
+          <t>Pretty Pets tenía productos y canales de venta, pero necesitaba que llegaran a ellos personas realmente interesadas en comprar para sus mascotas.</t>
         </is>
       </c>
     </row>
@@ -26549,7 +31422,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Para un estudiante, prepararse para un examen es una obligación; la marca tenía que hacerlo sentir más cercano y menos pesado.</t>
+          <t>Quien compra para su mascota compra con el corazón, y lo hace en los canales donde ya confía.</t>
         </is>
       </c>
     </row>
@@ -26561,7 +31434,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Naming, propuesta de valor, identidad visual, logo y colores, y un sistema de personajes que acompaña al estudiante y le da a la app personalidad más allá de la funcionalidad.</t>
+          <t>Una estrategia digital que parte de las mascotas y sus dueños, no del catálogo, y campañas de pauta segmentadas por intereses que llevan directo a sus canales de venta.</t>
         </is>
       </c>
     </row>
@@ -26573,7 +31446,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Los personajes le dan a una app algo que la funcionalidad sola no da: cercanía.</t>
+          <t>La pauta rinde más cuando lleva a la gente a donde ya compra, no a un canal nuevo.</t>
         </is>
       </c>
     </row>
@@ -26585,19 +31458,115 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Adobe Illustrator</t>
+          <t>Meta Ads</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
+          <t>Capacidades — Insight Lab</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Naming, Propuesta de valor, Identidad visual, Logo, Personajes</t>
+          <t>Estrategia digital, Pauta digital</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Medium Purple · #A778E7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Sandy Brown · #FABE65</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Khaki · #E3F78F</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Turquoise · #5CE1E6</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Dark Slate Blue · #2D4674</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>White · #FFFFFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "Aa"</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Quicksand</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "123"</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Quicksand</t>
         </is>
       </c>
     </row>
@@ -26612,7 +31581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -26639,7 +31608,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Seed Capital</t>
+          <t>Prepapp</t>
         </is>
       </c>
     </row>
@@ -26651,7 +31620,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Medios · Emprendimiento</t>
+          <t>Educación · Tecnología</t>
         </is>
       </c>
     </row>
@@ -26663,7 +31632,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>*Descubre* la semilla del éxito</t>
+          <t>Prepárate para la *siguiente etapa*</t>
         </is>
       </c>
     </row>
@@ -26675,7 +31644,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Podcast enfocado en emprendimiento.</t>
+          <t>Aplicación enfocada en la preparación para exámenes de Estado.</t>
         </is>
       </c>
     </row>
@@ -26687,7 +31656,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Seed Capital es un podcast de emprendimiento que necesitaba una marca con presencia propia frente a otros medios del sector. Trabajamos el naming, la propuesta de valor y el sistema de identidad visual (logo, colores y aplicaciones) pensados para funcionar tanto en el podcast como en sus redes y piezas de difusión.</t>
+          <t>Prepapp es una app enfocada en preparar estudiantes para exámenes de Estado. El reto no era solo la marca, sino construir un universo propio que la hiciera cercana a su público joven: naming, propuesta de valor, identidad visual, logo, colores y un sistema de personajes que le dieran personalidad a la app más allá de la funcionalidad.</t>
         </is>
       </c>
     </row>
@@ -26711,7 +31680,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Una semilla que se escucha.</t>
+          <t>Estudiar para el examen, pero con amigos.</t>
         </is>
       </c>
     </row>
@@ -26723,7 +31692,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Seed Capital es un podcast de emprendimiento que necesitaba una marca con presencia propia frente a otros medios del sector.</t>
+          <t>Prepapp es una app enfocada en preparar estudiantes para exámenes de Estado. El reto no era solo la marca, sino construir un universo propio que la hiciera cercana a su público joven.</t>
         </is>
       </c>
     </row>
@@ -26735,7 +31704,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Entre muchos podcasts de emprendimiento, lo que el público recuerda es la marca, no solo el tema.</t>
+          <t>Para un estudiante, prepararse para un examen es una obligación; la marca tenía que hacerlo sentir más cercano y menos pesado.</t>
         </is>
       </c>
     </row>
@@ -26747,7 +31716,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Naming, propuesta de valor y sistema de identidad visual (logo, colores y aplicaciones) pensados para funcionar tanto en el podcast como en sus redes y piezas de difusión.</t>
+          <t>Naming, propuesta de valor, identidad visual, logo y colores, y un sistema de personajes que acompaña al estudiante y le da a la app personalidad más allá de la funcionalidad.</t>
         </is>
       </c>
     </row>
@@ -26759,7 +31728,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Una identidad pensada desde el inicio para redes y piezas de difusión trabaja en todos los canales.</t>
+          <t>Los personajes le dan a una app algo que la funcionalidad sola no da: cercanía.</t>
         </is>
       </c>
     </row>
@@ -26783,7 +31752,67 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Naming, Propuesta de valor, Identidad visual, Piezas para redes</t>
+          <t>Naming, Propuesta de valor, Identidad visual, Logo, Personajes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Midnight Blue · #0C448E</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Goldenrod · #F6A728</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Goldenrod · #DD8B17</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "Aa"</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Fredoka</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "123"</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Fredoka</t>
         </is>
       </c>
     </row>
@@ -26798,7 +31827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -26825,7 +31854,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>AM Studios</t>
+          <t>Seed Capital</t>
         </is>
       </c>
     </row>
@@ -26837,7 +31866,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Marketing digital</t>
+          <t>Medios · Emprendimiento</t>
         </is>
       </c>
     </row>
@@ -26849,7 +31878,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Diseña *con datos*</t>
+          <t>*Descubre* la semilla del éxito</t>
         </is>
       </c>
     </row>
@@ -26861,7 +31890,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Agencia de marketing digital.</t>
+          <t>Podcast enfocado en emprendimiento.</t>
         </is>
       </c>
     </row>
@@ -26873,7 +31902,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Una agencia de marketing digital necesitaba verse tan sólida como sus resultados: logo, paleta de color e identidad visual construidos desde el naming.</t>
+          <t>Seed Capital es un podcast de emprendimiento que necesitaba una marca con presencia propia frente a otros medios del sector. Trabajamos el naming, la propuesta de valor y el sistema de identidad visual (logo, colores y aplicaciones) pensados para funcionar tanto en el podcast como en sus redes y piezas de difusión.</t>
         </is>
       </c>
     </row>
@@ -26897,7 +31926,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Diseñar con datos, y que se note.</t>
+          <t>Una semilla que se escucha.</t>
         </is>
       </c>
     </row>
@@ -26909,7 +31938,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>AM Studios es una agencia de marketing digital con buenos resultados, pero su marca no lo transmitía: necesitaba verse tan sólida como su trabajo.</t>
+          <t>Seed Capital es un podcast de emprendimiento que necesitaba una marca con presencia propia frente a otros medios del sector.</t>
         </is>
       </c>
     </row>
@@ -26921,7 +31950,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Una agencia que vende resultados no puede tener una marca improvisada.</t>
+          <t>Entre muchos podcasts de emprendimiento, lo que el público recuerda es la marca, no solo el tema.</t>
         </is>
       </c>
     </row>
@@ -26933,7 +31962,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Desde el naming, construimos el logo, la paleta de color y una identidad visual con un lenguaje que une diseño y datos.</t>
+          <t>Naming, propuesta de valor y sistema de identidad visual (logo, colores y aplicaciones) pensados para funcionar tanto en el podcast como en sus redes y piezas de difusión.</t>
         </is>
       </c>
     </row>
@@ -26945,7 +31974,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>La marca de una agencia es su primera muestra de trabajo.</t>
+          <t>Una identidad pensada desde el inicio para redes y piezas de difusión trabaja en todos los canales.</t>
         </is>
       </c>
     </row>
@@ -26969,7 +31998,103 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Logo, Paleta de color, Identidad visual</t>
+          <t>Naming, Propuesta de valor, Identidad visual, Piezas para redes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Sandy Brown · #FFBD58</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Dark Turquoise · #00C2CB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Olive Drab · #61B333</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>White Smoke · #F1F4F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Goldenrod · #D0CD08</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Dark Slate Gray · #2D4672</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "Aa"</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Open Sans</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "123"</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Montserrat</t>
         </is>
       </c>
     </row>
@@ -26984,7 +32109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -27011,7 +32136,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Tata's Photos</t>
+          <t>AM Studios</t>
         </is>
       </c>
     </row>
@@ -27023,7 +32148,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Fotografía</t>
+          <t>Marketing digital</t>
         </is>
       </c>
     </row>
@@ -27035,7 +32160,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Find the beauty *in the small things*</t>
+          <t>Diseña *con datos*</t>
         </is>
       </c>
     </row>
@@ -27047,7 +32172,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Marca personal de fotografía.</t>
+          <t>Agencia de marketing digital.</t>
         </is>
       </c>
     </row>
@@ -27059,7 +32184,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Marca personal para una fotógrafa: definimos su propuesta de valor y construimos el naming, los colores y la identidad que la representan.</t>
+          <t>Una agencia de marketing digital necesitaba verse tan sólida como sus resultados: logo, paleta de color e identidad visual construidos desde el naming.</t>
         </is>
       </c>
     </row>
@@ -27083,7 +32208,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Una marca tan detallista como su lente.</t>
+          <t>Diseñar con datos, y que se note.</t>
         </is>
       </c>
     </row>
@@ -27095,7 +32220,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Una fotógrafa que quería dejar de ser "una fotógrafa más" y tener una marca personal que la representara.</t>
+          <t>AM Studios es una agencia de marketing digital con buenos resultados, pero su marca no lo transmitía: necesitaba verse tan sólida como su trabajo.</t>
         </is>
       </c>
     </row>
@@ -27107,7 +32232,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>En fotografía, la gente contrata a la persona, no solo el servicio.</t>
+          <t>Una agencia que vende resultados no puede tener una marca improvisada.</t>
         </is>
       </c>
     </row>
@@ -27119,7 +32244,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Definimos su propuesta de valor y construimos el naming, los colores y una identidad inspirada en su forma de mirar: encontrar la belleza en las cosas pequeñas.</t>
+          <t>Desde el naming, construimos el logo, la paleta de color y una identidad visual con un lenguaje que une diseño y datos.</t>
         </is>
       </c>
     </row>
@@ -27131,19 +32256,115 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Una marca personal funciona cuando se parece a quien la lleva.</t>
+          <t>La marca de una agencia es su primera muestra de trabajo.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Capacidades — Brand &amp; Experience Lab</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Marca personal, Propuesta de valor, Naming, Identidad visual</t>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Logo, Paleta de color, Identidad visual</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Black · #000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Black · #212121</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Pink · #FFABD8</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>White · #FFFFFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Light Sky Blue · #86B0FF</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "Aa"</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Poppins</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "123"</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Poppins</t>
         </is>
       </c>
     </row>
@@ -28652,7 +33873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -28679,7 +33900,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Geco.</t>
+          <t>Tata's Photos</t>
         </is>
       </c>
     </row>
@@ -28691,7 +33912,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Comercio · Sostenibilidad</t>
+          <t>Fotografía</t>
         </is>
       </c>
     </row>
@@ -28703,7 +33924,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Get eco *like a geko*</t>
+          <t>Find the beauty *in the small things*</t>
         </is>
       </c>
     </row>
@@ -28715,7 +33936,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Tienda de productos ecológicos.</t>
+          <t>Marca personal de fotografía.</t>
         </is>
       </c>
     </row>
@@ -28727,7 +33948,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Identidad visual para una tienda de productos ecológicos, con una estrategia digital pensada para atraer a un público consciente.</t>
+          <t>Marca personal para una fotógrafa: definimos su propuesta de valor y construimos el naming, los colores y la identidad que la representan.</t>
         </is>
       </c>
     </row>
@@ -28739,7 +33960,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Identidad y diseño de marca · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+          <t>Estrategia de marca · Identidad y diseño de marca · Brand &amp; Experience Lab</t>
         </is>
       </c>
     </row>
@@ -28751,7 +33972,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Verde de verdad, no de discurso.</t>
+          <t>Una marca tan detallista como su lente.</t>
         </is>
       </c>
     </row>
@@ -28763,7 +33984,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Geco. vende productos ecológicos en un mercado donde muchas marcas dicen ser "verdes". Necesitaba atraer a un público consciente y lograr que ese interés terminara en una compra.</t>
+          <t>Una fotógrafa que quería dejar de ser "una fotógrafa más" y tener una marca personal que la representara.</t>
         </is>
       </c>
     </row>
@@ -28775,7 +33996,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>El público consciente desconfía de lo que es "verde" solo de palabra: necesita razones claras para elegir.</t>
+          <t>En fotografía, la gente contrata a la persona, no solo el servicio.</t>
         </is>
       </c>
     </row>
@@ -28787,7 +34008,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Una estrategia digital que explica con claridad por qué cada producto es una mejor elección, con un tono cercano y sin sermones, y un recorrido pensado para pasar del interés a la compra.</t>
+          <t>Definimos su propuesta de valor y construimos el naming, los colores y una identidad inspirada en su forma de mirar: encontrar la belleza en las cosas pequeñas.</t>
         </is>
       </c>
     </row>
@@ -28799,31 +34020,19 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>En lo sostenible, la coherencia vende más que el discurso.</t>
+          <t>Una marca personal funciona cuando se parece a quien la lleva.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Herramientas</t>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Shopify, Meta Ads, Google Ads</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Insight Lab</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Estrategia de marketing digital</t>
+          <t>Marca personal, Propuesta de valor, Naming, Identidad visual</t>
         </is>
       </c>
     </row>
@@ -28838,7 +34047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -28865,7 +34074,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Epika Store</t>
+          <t>Geco.</t>
         </is>
       </c>
     </row>
@@ -28877,7 +34086,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Comercio · Entretenimiento</t>
+          <t>Comercio · Sostenibilidad</t>
         </is>
       </c>
     </row>
@@ -28889,7 +34098,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Magia y estilo de *Disney* y *Universal*.</t>
+          <t>Get eco *like a geko*</t>
         </is>
       </c>
     </row>
@@ -28901,7 +34110,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Tienda de productos traídos de Disney Parks y Universal Studios en Orlando.</t>
+          <t>Tienda de productos ecológicos.</t>
         </is>
       </c>
     </row>
@@ -28913,7 +34122,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Desarrollo de logo, colores, sistema de identidad, tarjetas, texturas y diferentes aplicaciones de marca. Desarrollo de estrategia de marketing digital.</t>
+          <t>Identidad visual para una tienda de productos ecológicos, con una estrategia digital pensada para atraer a un público consciente.</t>
         </is>
       </c>
     </row>
@@ -28937,7 +34146,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Orlando, a un clic de distancia.</t>
+          <t>Verde de verdad, no de discurso.</t>
         </is>
       </c>
     </row>
@@ -28949,7 +34158,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Epika Store trae productos de Disney Parks y Universal Studios desde Orlando. Tenía un producto que enamora, pero necesitaba llegar a los fans y convertir ese entusiasmo en ventas.</t>
+          <t>Geco. vende productos ecológicos en un mercado donde muchas marcas dicen ser "verdes". Necesitaba atraer a un público consciente y lograr que ese interés terminara en una compra.</t>
         </is>
       </c>
     </row>
@@ -28961,7 +34170,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Sus clientes no buscan un producto: buscan un pedacito de la experiencia de los parques sin viajar a Orlando.</t>
+          <t>El público consciente desconfía de lo que es "verde" solo de palabra: necesita razones claras para elegir.</t>
         </is>
       </c>
     </row>
@@ -28973,7 +34182,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Todo el recorrido, desde el desarrollo de marca y el logo hasta el sitio, los posts para redes y la pauta digital: una estrategia que vende la experiencia antes que el objeto, con contenidos que evocan los parques y campañas dirigidas a fans de Disney y Universal.</t>
+          <t>Una estrategia digital que explica con claridad por qué cada producto es una mejor elección, con un tono cercano y sin sermones, y un recorrido pensado para pasar del interés a la compra.</t>
         </is>
       </c>
     </row>
@@ -28985,55 +34194,103 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Cuando el producto es emoción, la comunicación tiene que vender la experiencia, no el objeto.</t>
+          <t>En lo sostenible, la coherencia vende más que el discurso.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Botón "Ver sitio" (enlace)</t>
+          <t>Herramientas</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://www.lynka.io/s/epika-store</t>
+          <t>Shopify, Meta Ads, Google Ads</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Herramientas</t>
+          <t>Capacidades — Insight Lab</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Lynka, Meta Ads</t>
+          <t>Estrategia de marketing digital</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
+          <t>Paleta (popup) — nombre y código</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Desarrollo de marca, Logo, Sitio web</t>
+          <t>Dark Olive Green · #3F721D</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Capacidades — Insight Lab</t>
+          <t>Paleta (popup) — nombre y código</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de marketing digital, Contenido para redes, Pauta digital</t>
+          <t>Yellow Green · #74B053</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Yellow Green · #80CC29</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Dark Orange · #F58003</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Dark Slate Gray · #583B40</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>White Smoke · #F1F7F6</t>
         </is>
       </c>
     </row>
@@ -29075,7 +34332,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Centro del Sueño y Ronquido</t>
+          <t>Epika Store</t>
         </is>
       </c>
     </row>
@@ -29087,103 +34344,103 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Salud · Sueño</t>
+          <t>Comercio · Entretenimiento</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Descripción</t>
+          <t>Tagline</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Centro especializado en sueño en Medellín.</t>
+          <t>Magia y estilo de *Disney* y *Universal*.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Trabajo realizado</t>
+          <t>Descripción</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Sitio web, estrategia de marketing digital y pauta digital para un centro especializado en sueño en Medellín.</t>
+          <t>Tienda de productos traídos de Disney Parks y Universal Studios en Orlando.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Capacidades (card)</t>
+          <t>Trabajo realizado</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+          <t>Desarrollo de logo, colores, sistema de identidad, tarjetas, texturas y diferentes aplicaciones de marca. Desarrollo de estrategia de marketing digital.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>H2 (título del caso)</t>
+          <t>Capacidades (card)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Despiertos cuando alguien busca por qué ronca.</t>
+          <t>Identidad y diseño de marca · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Reto</t>
+          <t>H2 (título del caso)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>El Centro del Sueño y Ronquido es un centro especializado en Medellín. Necesitaba que las personas con problemas de sueño lo encontraran justo cuando empiezan a buscar respuestas.</t>
+          <t>Orlando, a un clic de distancia.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Reto</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Quien ronca o duerme mal suele buscar respuestas en internet antes de pedir una cita.</t>
+          <t>Epika Store trae productos de Disney Parks y Universal Studios desde Orlando. Tenía un producto que enamora, pero necesitaba llegar a los fans y convertir ese entusiasmo en ventas.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Qué construimos</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Un sitio web claro, pensado para resolver dudas y agendar; un blog con artículos sobre ronquido, apnea y trastornos del sueño optimizados para SEO; y pauta digital para llegar a pacientes en Medellín.</t>
+          <t>Sus clientes no buscan un producto: buscan un pedacito de la experiencia de los parques sin viajar a Orlando.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Qué construimos</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Subimos 58 puestos en el ranking de Google en menos de 3 semanas, con SEO, GEO, AEO y optimización de Google My Business.</t>
+          <t>Todo el recorrido, desde el desarrollo de marca y el logo hasta el sitio, los posts para redes y la pauta digital: una estrategia que vende la experiencia antes que el objeto, con contenidos que evocan los parques y campañas dirigidas a fans de Disney y Universal.</t>
         </is>
       </c>
     </row>
@@ -29195,7 +34452,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>En salud, un sitio claro y confiable es el primer paso de la consulta.</t>
+          <t>Cuando el producto es emoción, la comunicación tiene que vender la experiencia, no el objeto.</t>
         </is>
       </c>
     </row>
@@ -29207,7 +34464,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://www.clinicadelsuenoyronquido.com</t>
+          <t>https://www.lynka.io/s/epika-store</t>
         </is>
       </c>
     </row>
@@ -29219,7 +34476,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Wix, Semrush, Search Console, Google Analytics 4, Google My Business, Google Ads, Meta Ads</t>
+          <t>Lynka, Meta Ads</t>
         </is>
       </c>
     </row>
@@ -29231,7 +34488,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Sitio web</t>
+          <t>Desarrollo de marca, Logo, Sitio web</t>
         </is>
       </c>
     </row>
@@ -29243,7 +34500,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de marketing digital, Pauta digital, SEO, Blog y contenidos</t>
+          <t>Estrategia de marketing digital, Contenido para redes, Pauta digital</t>
         </is>
       </c>
     </row>
@@ -29253,6 +34510,696 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Centro del Sueño y Ronquido</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Salud · Sueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Centro especializado en sueño en Medellín.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Sitio web, estrategia de marketing digital y pauta digital para un centro especializado en sueño en Medellín.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Despiertos cuando alguien busca por qué ronca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>El Centro del Sueño y Ronquido es un centro especializado en Medellín. Necesitaba que las personas con problemas de sueño lo encontraran justo cuando empiezan a buscar respuestas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Quien ronca o duerme mal suele buscar respuestas en internet antes de pedir una cita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Un sitio web claro, pensado para resolver dudas y agendar; un blog con artículos sobre ronquido, apnea y trastornos del sueño optimizados para SEO; y pauta digital para llegar a pacientes en Medellín.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Subimos 58 puestos en el ranking de Google en menos de 3 semanas, con SEO, GEO, AEO y optimización de Google My Business.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>En salud, un sitio claro y confiable es el primer paso de la consulta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Botón "Ver sitio" (enlace)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clinicadelsuenoyronquido.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Wix, Semrush, Search Console, Google Analytics 4, Google My Business, Google Ads, Meta Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Sitio web</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Insight Lab</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marketing digital, Pauta digital, SEO, Blog y contenidos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Clínica del Cerebro</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Salud · Neurología</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Una mente sana *para un futuro brillante*</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Clínica neurológica en Medellín.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Rebranding, diseño de sitio web, estrategia de marketing digital y pauta digital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marca · Identidad y diseño de marca · Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Claridad para decisiones que pesan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>La Clínica del Cerebro atiende pacientes neurológicos en Medellín. Sus pacientes y sus familias llegan con dudas y preocupación, y la clínica necesitaba un canal digital que les diera confianza antes de la primera cita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Los pacientes y sus familias llegan con dudas y preocupación: necesitan información clara antes de agendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Un sitio web que explica sus servicios en lenguaje sencillo, contenido educativo para redes sociales sobre temas neurológicos y pauta digital para llegar a pacientes en Medellín.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>En salud, la confianza se construye con información útil, no con promesas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Wix, Meta Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Diseño web</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Insight Lab</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Estrategia de marketing digital, Pauta digital, Contenido para redes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Navy · #030083</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Turquoise · #5CE1E6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Teal · #004AAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Teal · #005281</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Sandy Brown · #FFBD58</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Paleta (popup) — nombre y código</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>White · #FFFFFF</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "Aa"</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Poppins</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Tipografía (popup) — muestra "123"</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Poppins</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Ravelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Consultoría de negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Tagline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Consultor de *estrategia de negocios*.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Consultor de estrategia de negocios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Marca personal para un consultor de estrategia de negocios: definimos su identidad visual para transmitir la misma solidez que su asesoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Identidad y diseño de marca · Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Solidez que se ve antes de la primera reunión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Carlos Ravelo es consultor de estrategia de negocios. En consultoría la primera impresión pesa: su marca tenía que transmitir la misma solidez que su asesoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Un consultor vende confianza antes de vender su asesoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Una identidad visual sobria y profesional, pensada para sus presentaciones, propuestas y redes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>La marca personal tiene que transmitir lo mismo que la persona en una reunión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Adobe Illustrator</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Marca personal, Identidad visual</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29285,7 +35232,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Clínica del Cerebro</t>
+          <t>Caminos de la Vida</t>
         </is>
       </c>
     </row>
@@ -29297,115 +35244,115 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Salud · Neurología</t>
+          <t>Salud · Cuidado del adulto mayor</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Tagline</t>
+          <t>Descripción</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Una mente sana *para un futuro brillante*</t>
+          <t>Hogar geriátrico.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Descripción</t>
+          <t>Trabajo realizado</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Clínica neurológica en Medellín.</t>
+          <t>Estrategia de marketing digital, pauta digital y desarrollo de sitio web para un hogar geriátrico.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Trabajo realizado</t>
+          <t>Capacidades (card)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Rebranding, diseño de sitio web, estrategia de marketing digital y pauta digital.</t>
+          <t>Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Capacidades (card)</t>
+          <t>H2 (título del caso)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de marca · Identidad y diseño de marca · Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+          <t>Tranquilidad para quien decide por amor.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>H2 (título del caso)</t>
+          <t>Reto</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Claridad para decisiones que pesan.</t>
+          <t>Caminos de la Vida es un hogar geriátrico. Elegir un hogar para un padre o una madre es una decisión difícil, y necesitaba que las familias lo encontraran y confiaran en él.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Reto</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>La Clínica del Cerebro atiende pacientes neurológicos en Medellín. Sus pacientes y sus familias llegan con dudas y preocupación, y la clínica necesitaba un canal digital que les diera confianza antes de la primera cita.</t>
+          <t>Quien decide casi nunca es el adulto mayor, sino su familia, y lo que busca es tranquilidad.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Qué construimos</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Los pacientes y sus familias llegan con dudas y preocupación: necesitan información clara antes de agendar.</t>
+          <t>Un sitio web que muestra el día a día del hogar y responde las preguntas de las familias, y una estrategia de marketing y pauta digital dirigida a hijos y familiares que están buscando opciones.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Qué construimos</t>
+          <t>Aprendizaje</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Un sitio web que explica sus servicios en lenguaje sencillo, contenido educativo para redes sociales sobre temas neurológicos y pauta digital para llegar a pacientes en Medellín.</t>
+          <t>Cuando la decisión es emocional, la comunicación tiene que hablarle a quien decide.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Aprendizaje</t>
+          <t>Botón "Ver sitio" (enlace)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>En salud, la confianza se construye con información útil, no con promesas.</t>
+          <t>https://www.hogarcaminosdelavida.com/</t>
         </is>
       </c>
     </row>
@@ -29417,7 +35364,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Wix, Meta Ads</t>
+          <t>Google Ads, Meta Ads</t>
         </is>
       </c>
     </row>
@@ -29429,7 +35376,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Diseño web</t>
+          <t>Desarrollo web</t>
         </is>
       </c>
     </row>
@@ -29441,577 +35388,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Estrategia de marketing digital, Pauta digital, Contenido para redes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="120" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Contenido exacto</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>H1 (nombre del proyecto)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Carlos Ravelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Categoría</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Consultoría de negocios</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Tagline</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Consultor de *estrategia de negocios*.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Consultor de estrategia de negocios.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Trabajo realizado</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Marca personal para un consultor de estrategia de negocios: definimos su identidad visual para transmitir la misma solidez que su asesoría.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades (card)</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Identidad y diseño de marca · Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Solidez que se ve antes de la primera reunión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Carlos Ravelo es consultor de estrategia de negocios. En consultoría la primera impresión pesa: su marca tenía que transmitir la misma solidez que su asesoría.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Un consultor vende confianza antes de vender su asesoría.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Una identidad visual sobria y profesional, pensada para sus presentaciones, propuestas y redes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>La marca personal tiene que transmitir lo mismo que la persona en una reunión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Adobe Illustrator</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Marca personal, Identidad visual</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="120" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Contenido exacto</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>H1 (nombre del proyecto)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Caminos de la Vida</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Categoría</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Salud · Cuidado del adulto mayor</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Hogar geriátrico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Trabajo realizado</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Estrategia de marketing digital, pauta digital y desarrollo de sitio web para un hogar geriátrico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades (card)</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Tranquilidad para quien decide por amor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Caminos de la Vida es un hogar geriátrico. Elegir un hogar para un padre o una madre es una decisión difícil, y necesitaba que las familias lo encontraran y confiaran en él.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Quien decide casi nunca es el adulto mayor, sino su familia, y lo que busca es tranquilidad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Un sitio web que muestra el día a día del hogar y responde las preguntas de las familias, y una estrategia de marketing y pauta digital dirigida a hijos y familiares que están buscando opciones.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Cuando la decisión es emocional, la comunicación tiene que hablarle a quien decide.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Botón "Ver sitio" (enlace)</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hogarcaminosdelavida.com/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Google Ads, Meta Ads</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Desarrollo web</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Insight Lab</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
           <t>Estrategia de marketing digital, Pauta digital</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="120" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Contenido exacto</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>H1 (nombre del proyecto)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>La Marquessa</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Categoría</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Moda · Accesorios</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Tienda de accesorios.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Trabajo realizado</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Optimizamos el sitio web de esta tienda de accesorios y diseñamos la estrategia de pauta digital para impulsar sus ventas online.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades (card)</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>H2 (título del caso)</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Primero la vitrina, después la fila.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Reto</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>La Marquessa ya vendía accesorios en su tienda en línea y quería vender más. Invertir en pauta sin revisar el sitio era arriesgarse a pagar por visitas que no compran.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Llevar más visitas a un sitio que no está listo para vender es pagar dos veces: primero había que ajustar el sitio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Qué construimos</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Optimizamos el sitio para que comprar fuera más fácil (navegación, fichas de producto y proceso de compra) y después diseñamos una estrategia de pauta digital para llevar tráfico a una tienda lista para vender.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Aprendizaje</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Primero se optimiza la tienda, después se invierte en pauta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Herramientas</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Vercel, GitHub, Google My Business, Meta Ads</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Brand &amp; Experience Lab</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Optimización del sitio web</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Capacidades — Insight Lab</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Pauta digital</t>
         </is>
       </c>
     </row>
@@ -30053,7 +35430,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Ser Niños</t>
+          <t>La Marquessa</t>
         </is>
       </c>
     </row>
@@ -30065,7 +35442,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Comercio · Educación</t>
+          <t>Moda · Accesorios</t>
         </is>
       </c>
     </row>
@@ -30077,7 +35454,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Tienda de juguetes y educación consciente.</t>
+          <t>Tienda de accesorios.</t>
         </is>
       </c>
     </row>
@@ -30089,7 +35466,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Ajustes al sitio web y una estrategia de pauta digital enfocada en un solo objetivo: que esta tienda de juguetes venda más.</t>
+          <t>Optimizamos el sitio web de esta tienda de accesorios y diseñamos la estrategia de pauta digital para impulsar sus ventas online.</t>
         </is>
       </c>
     </row>
@@ -30113,7 +35490,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Un solo juego: vender más.</t>
+          <t>Primero la vitrina, después la fila.</t>
         </is>
       </c>
     </row>
@@ -30125,7 +35502,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Ser Niños es una tienda de juguetes y educación consciente con sitio propio. Su objetivo era claro: vender más en línea.</t>
+          <t>La Marquessa ya vendía accesorios en su tienda en línea y quería vender más. Invertir en pauta sin revisar el sitio era arriesgarse a pagar por visitas que no compran.</t>
         </is>
       </c>
     </row>
@@ -30137,7 +35514,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Las familias que buscan juguetes conscientes investigan antes de comprar: el sitio tenía que resolver sus dudas rápido.</t>
+          <t>Llevar más visitas a un sitio que no está listo para vender es pagar dos veces: primero había que ajustar el sitio.</t>
         </is>
       </c>
     </row>
@@ -30149,7 +35526,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Ajustes puntuales al sitio para que las familias encuentren rápido lo que buscan y entiendan el valor de cada juguete, y una estrategia de pauta digital medida contra un solo objetivo: las ventas.</t>
+          <t>Optimizamos el sitio para que comprar fuera más fácil (navegación, fichas de producto y proceso de compra) y después diseñamos una estrategia de pauta digital para llevar tráfico a una tienda lista para vender.</t>
         </is>
       </c>
     </row>
@@ -30161,7 +35538,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Un solo objetivo hace que cada ajuste y cada peso de pauta se midan contra lo mismo.</t>
+          <t>Primero se optimiza la tienda, después se invierte en pauta.</t>
         </is>
       </c>
     </row>
@@ -30185,7 +35562,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Ajustes al sitio web</t>
+          <t>Optimización del sitio web</t>
         </is>
       </c>
     </row>
@@ -30212,7 +35589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -30239,7 +35616,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Acústica EAFIT</t>
+          <t>Ser Niños</t>
         </is>
       </c>
     </row>
@@ -30251,7 +35628,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Sitio web</t>
+          <t>Comercio · Educación</t>
         </is>
       </c>
     </row>
@@ -30263,19 +35640,127 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Sitio web desarrollado en WordPress.</t>
+          <t>Tienda de juguetes y educación consciente.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>Trabajo realizado</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Ajustes al sitio web y una estrategia de pauta digital enfocada en un solo objetivo: que esta tienda de juguetes venda más.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>Capacidades (card)</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>H2 (título del caso)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Un solo juego: vender más.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Reto</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Ser Niños es una tienda de juguetes y educación consciente con sitio propio. Su objetivo era claro: vender más en línea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Las familias que buscan juguetes conscientes investigan antes de comprar: el sitio tenía que resolver sus dudas rápido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Qué construimos</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Ajustes puntuales al sitio para que las familias encuentren rápido lo que buscan y entiendan el valor de cada juguete, y una estrategia de pauta digital medida contra un solo objetivo: las ventas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Aprendizaje</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Un solo objetivo hace que cada ajuste y cada peso de pauta se midan contra lo mismo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Herramientas</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Vercel, GitHub, Google My Business, Meta Ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Brand &amp; Experience Lab</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Ajustes al sitio web</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades — Insight Lab</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Pauta digital</t>
         </is>
       </c>
     </row>
@@ -30317,7 +35802,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Christmas House</t>
+          <t>Acústica EAFIT</t>
         </is>
       </c>
     </row>
@@ -30329,7 +35814,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Comercio</t>
+          <t>Sitio web</t>
         </is>
       </c>
     </row>
@@ -30341,7 +35826,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Tienda en línea con pauta digital.</t>
+          <t>Sitio web desarrollado en WordPress.</t>
         </is>
       </c>
     </row>
@@ -31898,6 +37383,84 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Contenido exacto</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>H1 (nombre del proyecto)</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Christmas House</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Categoría</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Comercio</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Tienda en línea con pauta digital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Capacidades (card)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Experiencia digital · Crecimiento y marketing digital · Brand &amp; Experience Lab · Insight Lab</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
